--- a/examples/ashare-bull-stock-study/results/codex_cross_check/template_20260828.xlsx
+++ b/examples/ashare-bull-stock-study/results/codex_cross_check/template_20260828.xlsx
@@ -1673,7 +1673,7 @@
       <c r="Q4" s="18" t="n"/>
       <c r="R4" s="18" t="n"/>
       <c r="S4" s="18" t="n">
-        <v>0.4895861422870816</v>
+        <v>0.5837573822135189</v>
       </c>
       <c r="T4" s="17" t="n">
         <v>4.082244427363567</v>
@@ -1863,7 +1863,7 @@
       <c r="Q6" s="18" t="n"/>
       <c r="R6" s="18" t="n"/>
       <c r="S6" s="18" t="n">
-        <v>0.5239623663284239</v>
+        <v>0.6201614099953963</v>
       </c>
       <c r="T6" s="17" t="n">
         <v>2.980633802816901</v>
@@ -1945,9 +1945,9 @@
       <c r="M7" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N7" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O7" s="16" t="inlineStr">
@@ -1959,7 +1959,7 @@
       <c r="Q7" s="18" t="n"/>
       <c r="R7" s="18" t="n"/>
       <c r="S7" s="18" t="n">
-        <v>0.6687779376330308</v>
+        <v>0.7263079468804343</v>
       </c>
       <c r="T7" s="17" t="n">
         <v>1.51937984496124</v>
@@ -2041,9 +2041,9 @@
       <c r="M8" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N8" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O8" s="16" t="inlineStr">
@@ -2054,9 +2054,7 @@
       <c r="P8" s="17" t="n"/>
       <c r="Q8" s="18" t="n"/>
       <c r="R8" s="18" t="n"/>
-      <c r="S8" s="18" t="n">
-        <v>0.5676409784883759</v>
-      </c>
+      <c r="S8" s="18" t="n"/>
       <c r="T8" s="17" t="n">
         <v>1.536647546207776</v>
       </c>
@@ -2795,9 +2793,9 @@
       <c r="M16" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N16" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N16" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O16" s="16" t="inlineStr">
@@ -2808,9 +2806,7 @@
       <c r="P16" s="17" t="n"/>
       <c r="Q16" s="18" t="n"/>
       <c r="R16" s="18" t="n"/>
-      <c r="S16" s="18" t="n">
-        <v>0.3702713508753387</v>
-      </c>
+      <c r="S16" s="18" t="n"/>
       <c r="T16" s="17" t="n">
         <v>1.104991394148021</v>
       </c>
@@ -2905,7 +2901,7 @@
       <c r="Q17" s="18" t="n"/>
       <c r="R17" s="18" t="n"/>
       <c r="S17" s="18" t="n">
-        <v>0.4492886599051275</v>
+        <v>0.4088234026266369</v>
       </c>
       <c r="T17" s="17" t="n">
         <v>1.086336965632858</v>
@@ -3095,7 +3091,7 @@
       <c r="Q19" s="18" t="n"/>
       <c r="R19" s="18" t="n"/>
       <c r="S19" s="18" t="n">
-        <v>0.5965111936858178</v>
+        <v>0.6371539804909452</v>
       </c>
       <c r="T19" s="17" t="n">
         <v>1.896900695762176</v>
@@ -3191,7 +3187,7 @@
       <c r="Q20" s="18" t="n"/>
       <c r="R20" s="18" t="n"/>
       <c r="S20" s="18" t="n">
-        <v>0.5979408879300834</v>
+        <v>0.6013077453742562</v>
       </c>
       <c r="T20" s="17" t="n">
         <v>0.8249275362318842</v>
@@ -3739,9 +3735,9 @@
       <c r="M26" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N26" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O26" s="16" t="inlineStr">
@@ -3753,7 +3749,7 @@
       <c r="Q26" s="18" t="n"/>
       <c r="R26" s="18" t="n"/>
       <c r="S26" s="18" t="n">
-        <v>0.5826984331582912</v>
+        <v>0.7669284215878287</v>
       </c>
       <c r="T26" s="17" t="n">
         <v>0.8091482649842272</v>
@@ -3943,7 +3939,7 @@
       <c r="Q28" s="18" t="n"/>
       <c r="R28" s="18" t="n"/>
       <c r="S28" s="18" t="n">
-        <v>0.7928934063453984</v>
+        <v>0.7539224538527445</v>
       </c>
       <c r="T28" s="17" t="n">
         <v>1.046269278866195</v>
@@ -4133,7 +4129,7 @@
       <c r="Q30" s="18" t="n"/>
       <c r="R30" s="18" t="n"/>
       <c r="S30" s="18" t="n">
-        <v>0.5489475379859726</v>
+        <v>0.48273361872466</v>
       </c>
       <c r="T30" s="17" t="n">
         <v>1.129465748934775</v>
@@ -4229,7 +4225,7 @@
       <c r="Q31" s="18" t="n"/>
       <c r="R31" s="18" t="n"/>
       <c r="S31" s="18" t="n">
-        <v>0.6874798744570032</v>
+        <v>0.6164276829751248</v>
       </c>
       <c r="T31" s="17" t="n">
         <v>2.232172470978441</v>
@@ -4419,7 +4415,7 @@
       <c r="Q33" s="18" t="n"/>
       <c r="R33" s="18" t="n"/>
       <c r="S33" s="18" t="n">
-        <v>0.5680562237521595</v>
+        <v>0.6488825946202985</v>
       </c>
       <c r="T33" s="17" t="n">
         <v>0.5992578849721706</v>
@@ -4501,9 +4497,9 @@
       <c r="M34" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N34" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N34" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O34" s="16" t="inlineStr">
@@ -4514,7 +4510,9 @@
       <c r="P34" s="17" t="n"/>
       <c r="Q34" s="18" t="n"/>
       <c r="R34" s="18" t="n"/>
-      <c r="S34" s="18" t="n"/>
+      <c r="S34" s="18" t="n">
+        <v>0.3479216171436539</v>
+      </c>
       <c r="T34" s="17" t="n">
         <v>0.8013483146067415</v>
       </c>
@@ -4609,7 +4607,7 @@
       <c r="Q35" s="18" t="n"/>
       <c r="R35" s="18" t="n"/>
       <c r="S35" s="18" t="n">
-        <v>0.5298086629929519</v>
+        <v>0.5516922261144585</v>
       </c>
       <c r="T35" s="17" t="n">
         <v>0.5971049457177324</v>
@@ -4705,7 +4703,7 @@
       <c r="Q36" s="18" t="n"/>
       <c r="R36" s="18" t="n"/>
       <c r="S36" s="18" t="n">
-        <v>0.4579627965972348</v>
+        <v>0.3885884492791233</v>
       </c>
       <c r="T36" s="17" t="n">
         <v>1.854568854568855</v>
@@ -4787,9 +4785,9 @@
       <c r="M37" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N37" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N37" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O37" s="16" t="inlineStr">
@@ -4800,7 +4798,9 @@
       <c r="P37" s="17" t="n"/>
       <c r="Q37" s="18" t="n"/>
       <c r="R37" s="18" t="n"/>
-      <c r="S37" s="18" t="n"/>
+      <c r="S37" s="18" t="n">
+        <v>0.3179014583720582</v>
+      </c>
       <c r="T37" s="17" t="n">
         <v>0.918032786885246</v>
       </c>
@@ -4881,9 +4881,9 @@
       <c r="M38" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N38" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N38" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O38" s="16" t="inlineStr">
@@ -4895,7 +4895,7 @@
       <c r="Q38" s="18" t="n"/>
       <c r="R38" s="18" t="n"/>
       <c r="S38" s="18" t="n">
-        <v>0.7087262728717952</v>
+        <v>0.6383737152365203</v>
       </c>
       <c r="T38" s="17" t="n">
         <v>0.7993943981831944</v>
@@ -5171,7 +5171,7 @@
       <c r="Q41" s="18" t="n"/>
       <c r="R41" s="18" t="n"/>
       <c r="S41" s="18" t="n">
-        <v>0.3493201231905405</v>
+        <v>0.3602608494594197</v>
       </c>
       <c r="T41" s="17" t="n">
         <v>0.8201233981964879</v>
@@ -5267,7 +5267,7 @@
       <c r="Q42" s="18" t="n"/>
       <c r="R42" s="18" t="n"/>
       <c r="S42" s="18" t="n">
-        <v>0.5185861677186915</v>
+        <v>0.5001515439224913</v>
       </c>
       <c r="T42" s="17" t="n">
         <v>0.8588977797813591</v>
@@ -5363,7 +5363,7 @@
       <c r="Q43" s="18" t="n"/>
       <c r="R43" s="18" t="n"/>
       <c r="S43" s="18" t="n">
-        <v>0.7897383614491162</v>
+        <v>0.7810968059819697</v>
       </c>
       <c r="T43" s="17" t="n">
         <v>0.5729337391711544</v>
@@ -5539,9 +5539,9 @@
       <c r="M45" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N45" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N45" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O45" s="16" t="inlineStr">
@@ -5552,7 +5552,9 @@
       <c r="P45" s="17" t="n"/>
       <c r="Q45" s="18" t="n"/>
       <c r="R45" s="18" t="n"/>
-      <c r="S45" s="18" t="n"/>
+      <c r="S45" s="18" t="n">
+        <v>0.460140872072592</v>
+      </c>
       <c r="T45" s="17" t="n">
         <v>1.280750137892995</v>
       </c>
@@ -5741,7 +5743,7 @@
       <c r="Q47" s="18" t="n"/>
       <c r="R47" s="18" t="n"/>
       <c r="S47" s="18" t="n">
-        <v>0.4486711006782491</v>
+        <v>0.4396916957463503</v>
       </c>
       <c r="T47" s="17" t="n">
         <v>0.4559999999999999</v>
@@ -5823,9 +5825,9 @@
       <c r="M48" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N48" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N48" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O48" s="16" t="inlineStr">
@@ -5837,7 +5839,7 @@
       <c r="Q48" s="18" t="n"/>
       <c r="R48" s="18" t="n"/>
       <c r="S48" s="18" t="n">
-        <v>0.6499942501733138</v>
+        <v>0.8207130606863607</v>
       </c>
       <c r="T48" s="17" t="n">
         <v>3.06290672451193</v>
@@ -5933,7 +5935,7 @@
       <c r="Q49" s="18" t="n"/>
       <c r="R49" s="18" t="n"/>
       <c r="S49" s="18" t="n">
-        <v>0.6864606144513272</v>
+        <v>0.6430711912021507</v>
       </c>
       <c r="T49" s="17" t="n">
         <v>1.116422513492675</v>
@@ -6029,7 +6031,7 @@
       <c r="Q50" s="18" t="n"/>
       <c r="R50" s="18" t="n"/>
       <c r="S50" s="18" t="n">
-        <v>0.3832366987160346</v>
+        <v>0.3709518559680663</v>
       </c>
       <c r="T50" s="17" t="n">
         <v>0.6371191135734073</v>
@@ -6125,7 +6127,7 @@
       <c r="Q51" s="18" t="n"/>
       <c r="R51" s="18" t="n"/>
       <c r="S51" s="18" t="n">
-        <v>0.7107489133768511</v>
+        <v>0.8091996947698779</v>
       </c>
       <c r="T51" s="17" t="n">
         <v>1.266488413547237</v>
@@ -6315,7 +6317,7 @@
       <c r="Q53" s="18" t="n"/>
       <c r="R53" s="18" t="n"/>
       <c r="S53" s="18" t="n">
-        <v>0.8380549899558498</v>
+        <v>0.8402116178044428</v>
       </c>
       <c r="T53" s="17" t="n">
         <v>0.5861386138613862</v>
@@ -6411,7 +6413,7 @@
       <c r="Q54" s="18" t="n"/>
       <c r="R54" s="18" t="n"/>
       <c r="S54" s="18" t="n">
-        <v>0.70127890276442</v>
+        <v>0.7195458722834124</v>
       </c>
       <c r="T54" s="17" t="n">
         <v>0.423160173160173</v>
@@ -6507,7 +6509,7 @@
       <c r="Q55" s="18" t="n"/>
       <c r="R55" s="18" t="n"/>
       <c r="S55" s="18" t="n">
-        <v>0.6359166147168913</v>
+        <v>0.5599731114578178</v>
       </c>
       <c r="T55" s="17" t="n">
         <v>0.43733153638814</v>
@@ -6589,9 +6591,9 @@
       <c r="M56" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N56" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N56" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O56" s="16" t="inlineStr">
@@ -6603,7 +6605,7 @@
       <c r="Q56" s="18" t="n"/>
       <c r="R56" s="18" t="n"/>
       <c r="S56" s="18" t="n">
-        <v>0.7089553123233314</v>
+        <v>0.6690339461096686</v>
       </c>
       <c r="T56" s="17" t="n">
         <v>0.700486448922863</v>
@@ -6699,7 +6701,7 @@
       <c r="Q57" s="18" t="n"/>
       <c r="R57" s="18" t="n"/>
       <c r="S57" s="18" t="n">
-        <v>0.5251063900850369</v>
+        <v>0.4749133011867396</v>
       </c>
       <c r="T57" s="17" t="n">
         <v>0.5272340425531916</v>
@@ -6795,7 +6797,7 @@
       <c r="Q58" s="18" t="n"/>
       <c r="R58" s="18" t="n"/>
       <c r="S58" s="18" t="n">
-        <v>0.2602566029072812</v>
+        <v>0.1546277792513661</v>
       </c>
       <c r="T58" s="17" t="n">
         <v>1.593871595330739</v>
@@ -6985,7 +6987,7 @@
       <c r="Q60" s="18" t="n"/>
       <c r="R60" s="18" t="n"/>
       <c r="S60" s="18" t="n">
-        <v>0.5751183088804795</v>
+        <v>0.5179287585060368</v>
       </c>
       <c r="T60" s="17" t="n">
         <v>0.6898263027295284</v>
@@ -7081,7 +7083,7 @@
       <c r="Q61" s="18" t="n"/>
       <c r="R61" s="18" t="n"/>
       <c r="S61" s="18" t="n">
-        <v>0.5873113541283496</v>
+        <v>0.3144685659740958</v>
       </c>
       <c r="T61" s="17" t="n">
         <v>0.7827248441674086</v>
@@ -7173,7 +7175,7 @@
       <c r="Q62" s="18" t="n"/>
       <c r="R62" s="18" t="n"/>
       <c r="S62" s="18" t="n">
-        <v>0.4644701407156103</v>
+        <v>0.4528000208854522</v>
       </c>
       <c r="T62" s="17" t="n">
         <v>0.5521739130434784</v>
@@ -7269,7 +7271,7 @@
       <c r="Q63" s="18" t="n"/>
       <c r="R63" s="18" t="n"/>
       <c r="S63" s="18" t="n">
-        <v>0.7390827440060777</v>
+        <v>0.7391739146520225</v>
       </c>
       <c r="T63" s="17" t="n">
         <v>0.5376696303228825</v>
@@ -7365,7 +7367,7 @@
       <c r="Q64" s="18" t="n"/>
       <c r="R64" s="18" t="n"/>
       <c r="S64" s="18" t="n">
-        <v>0.3996871580391046</v>
+        <v>0.4505335429163548</v>
       </c>
       <c r="T64" s="17" t="n">
         <v>0.8261376896149359</v>
@@ -7551,7 +7553,7 @@
       <c r="Q66" s="18" t="n"/>
       <c r="R66" s="18" t="n"/>
       <c r="S66" s="18" t="n">
-        <v>0.4485279789269557</v>
+        <v>0.6359324328828446</v>
       </c>
       <c r="T66" s="17" t="n">
         <v>0.4685191698909603</v>
@@ -7633,9 +7635,9 @@
       <c r="M67" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N67" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N67" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O67" s="16" t="inlineStr">
@@ -7647,7 +7649,7 @@
       <c r="Q67" s="18" t="n"/>
       <c r="R67" s="18" t="n"/>
       <c r="S67" s="18" t="n">
-        <v>0.5721992649149387</v>
+        <v>0.7112214091586997</v>
       </c>
       <c r="T67" s="17" t="n">
         <v>1.049306625577812</v>
@@ -7743,7 +7745,7 @@
       <c r="Q68" s="18" t="n"/>
       <c r="R68" s="18" t="n"/>
       <c r="S68" s="18" t="n">
-        <v>0.341223904818644</v>
+        <v>0.4679357761128102</v>
       </c>
       <c r="T68" s="17" t="n">
         <v>0.4529217627645119</v>
@@ -8027,7 +8029,7 @@
       <c r="Q71" s="18" t="n"/>
       <c r="R71" s="18" t="n"/>
       <c r="S71" s="18" t="n">
-        <v>0.4006195882175567</v>
+        <v>0.5563691861057682</v>
       </c>
       <c r="T71" s="17" t="n">
         <v>0.6445047489823608</v>
@@ -8123,7 +8125,7 @@
       <c r="Q72" s="18" t="n"/>
       <c r="R72" s="18" t="n"/>
       <c r="S72" s="18" t="n">
-        <v>0.8159473846553051</v>
+        <v>0.8048734007659614</v>
       </c>
       <c r="T72" s="17" t="n">
         <v>1.160136286201022</v>
@@ -8219,7 +8221,7 @@
       <c r="Q73" s="18" t="n"/>
       <c r="R73" s="18" t="n"/>
       <c r="S73" s="18" t="n">
-        <v>0.367917833091275</v>
+        <v>0.5350119024669122</v>
       </c>
       <c r="T73" s="17" t="n">
         <v>0.8682745825602971</v>
@@ -8503,7 +8505,7 @@
       <c r="Q76" s="18" t="n"/>
       <c r="R76" s="18" t="n"/>
       <c r="S76" s="18" t="n">
-        <v>0.2738600116562628</v>
+        <v>0.2820060101901576</v>
       </c>
       <c r="T76" s="17" t="n">
         <v>0.8571834992887626</v>
@@ -8585,9 +8587,9 @@
       <c r="M77" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N77" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N77" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O77" s="16" t="inlineStr">
@@ -8599,7 +8601,7 @@
       <c r="Q77" s="18" t="n"/>
       <c r="R77" s="18" t="n"/>
       <c r="S77" s="18" t="n">
-        <v>0.6746286573561653</v>
+        <v>0.756322091248415</v>
       </c>
       <c r="T77" s="17" t="n">
         <v>1.130935251798561</v>
@@ -8695,7 +8697,7 @@
       <c r="Q78" s="18" t="n"/>
       <c r="R78" s="18" t="n"/>
       <c r="S78" s="18" t="n">
-        <v>0.4359681587812185</v>
+        <v>0.412536660645403</v>
       </c>
       <c r="T78" s="17" t="n">
         <v>0.6416131989000917</v>
@@ -8871,9 +8873,9 @@
       <c r="M80" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N80" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N80" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O80" s="16" t="inlineStr">
@@ -8884,7 +8886,9 @@
       <c r="P80" s="17" t="n"/>
       <c r="Q80" s="18" t="n"/>
       <c r="R80" s="18" t="n"/>
-      <c r="S80" s="18" t="n"/>
+      <c r="S80" s="18" t="n">
+        <v>0.5539922794159842</v>
+      </c>
       <c r="T80" s="17" t="n">
         <v>0.4933774834437086</v>
       </c>
@@ -8979,7 +8983,7 @@
       <c r="Q81" s="18" t="n"/>
       <c r="R81" s="18" t="n"/>
       <c r="S81" s="18" t="n">
-        <v>0.5845577479744137</v>
+        <v>0.551363436926618</v>
       </c>
       <c r="T81" s="17" t="n">
         <v>0.420997375328084</v>
@@ -9155,9 +9159,9 @@
       <c r="M83" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N83" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N83" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O83" s="16" t="inlineStr">
@@ -9175,7 +9179,7 @@
         <v>0.8584378</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>0.7040862588423586</v>
+        <v>0.6292848239662183</v>
       </c>
       <c r="T83" s="17" t="n">
         <v>0.4898828541001063</v>
@@ -9257,9 +9261,9 @@
       <c r="M84" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N84" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N84" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O84" s="16" t="inlineStr">
@@ -9271,7 +9275,7 @@
       <c r="Q84" s="18" t="n"/>
       <c r="R84" s="18" t="n"/>
       <c r="S84" s="18" t="n">
-        <v>0.6053347250509514</v>
+        <v>0.7228236767824699</v>
       </c>
       <c r="T84" s="17" t="n">
         <v>0.7576736672051696</v>
@@ -9367,7 +9371,7 @@
       <c r="Q85" s="18" t="n"/>
       <c r="R85" s="18" t="n"/>
       <c r="S85" s="18" t="n">
-        <v>0.6830194087786177</v>
+        <v>0.6141862423499979</v>
       </c>
       <c r="T85" s="17" t="n">
         <v>0.8475120385232744</v>
@@ -9744,9 +9748,9 @@
       <c r="M4" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N4" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O4" s="14" t="inlineStr">
@@ -9764,7 +9768,7 @@
         <v>0.61080986</v>
       </c>
       <c r="S4" s="18" t="n">
-        <v>0.7558045131122967</v>
+        <v>0.6807571589528316</v>
       </c>
       <c r="T4" s="17" t="n">
         <v>0.1275347906978474</v>
@@ -10253,7 +10257,7 @@
       <c r="Q4" s="18" t="n"/>
       <c r="R4" s="18" t="n"/>
       <c r="S4" s="18" t="n">
-        <v>0.4895861422870816</v>
+        <v>0.5837573822135189</v>
       </c>
       <c r="T4" s="17" t="n">
         <v>4.082244427363567</v>
@@ -10443,7 +10447,7 @@
       <c r="Q6" s="18" t="n"/>
       <c r="R6" s="18" t="n"/>
       <c r="S6" s="18" t="n">
-        <v>0.5239623663284239</v>
+        <v>0.6201614099953963</v>
       </c>
       <c r="T6" s="17" t="n">
         <v>2.980633802816901</v>
@@ -10525,9 +10529,9 @@
       <c r="M7" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N7" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O7" s="16" t="inlineStr">
@@ -10539,7 +10543,7 @@
       <c r="Q7" s="18" t="n"/>
       <c r="R7" s="18" t="n"/>
       <c r="S7" s="18" t="n">
-        <v>0.6687779376330308</v>
+        <v>0.7263079468804343</v>
       </c>
       <c r="T7" s="17" t="n">
         <v>1.51937984496124</v>
@@ -10621,9 +10625,9 @@
       <c r="M8" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N8" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O8" s="16" t="inlineStr">
@@ -10634,9 +10638,7 @@
       <c r="P8" s="17" t="n"/>
       <c r="Q8" s="18" t="n"/>
       <c r="R8" s="18" t="n"/>
-      <c r="S8" s="18" t="n">
-        <v>0.5676409784883759</v>
-      </c>
+      <c r="S8" s="18" t="n"/>
       <c r="T8" s="17" t="n">
         <v>1.536647546207776</v>
       </c>
@@ -11375,9 +11377,9 @@
       <c r="M16" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N16" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N16" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O16" s="16" t="inlineStr">
@@ -11388,9 +11390,7 @@
       <c r="P16" s="17" t="n"/>
       <c r="Q16" s="18" t="n"/>
       <c r="R16" s="18" t="n"/>
-      <c r="S16" s="18" t="n">
-        <v>0.3702713508753387</v>
-      </c>
+      <c r="S16" s="18" t="n"/>
       <c r="T16" s="17" t="n">
         <v>1.104991394148021</v>
       </c>
@@ -11485,7 +11485,7 @@
       <c r="Q17" s="18" t="n"/>
       <c r="R17" s="18" t="n"/>
       <c r="S17" s="18" t="n">
-        <v>0.4492886599051275</v>
+        <v>0.4088234026266369</v>
       </c>
       <c r="T17" s="17" t="n">
         <v>1.086336965632858</v>
@@ -11675,7 +11675,7 @@
       <c r="Q19" s="18" t="n"/>
       <c r="R19" s="18" t="n"/>
       <c r="S19" s="18" t="n">
-        <v>0.5965111936858178</v>
+        <v>0.6371539804909452</v>
       </c>
       <c r="T19" s="17" t="n">
         <v>1.896900695762176</v>
@@ -11771,7 +11771,7 @@
       <c r="Q20" s="18" t="n"/>
       <c r="R20" s="18" t="n"/>
       <c r="S20" s="18" t="n">
-        <v>0.5979408879300834</v>
+        <v>0.6013077453742562</v>
       </c>
       <c r="T20" s="17" t="n">
         <v>0.8249275362318842</v>
@@ -12319,9 +12319,9 @@
       <c r="M26" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N26" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O26" s="16" t="inlineStr">
@@ -12333,7 +12333,7 @@
       <c r="Q26" s="18" t="n"/>
       <c r="R26" s="18" t="n"/>
       <c r="S26" s="18" t="n">
-        <v>0.5826984331582912</v>
+        <v>0.7669284215878287</v>
       </c>
       <c r="T26" s="17" t="n">
         <v>0.8091482649842272</v>
@@ -12523,7 +12523,7 @@
       <c r="Q28" s="18" t="n"/>
       <c r="R28" s="18" t="n"/>
       <c r="S28" s="18" t="n">
-        <v>0.7928934063453984</v>
+        <v>0.7539224538527445</v>
       </c>
       <c r="T28" s="17" t="n">
         <v>1.046269278866195</v>
@@ -12713,7 +12713,7 @@
       <c r="Q30" s="18" t="n"/>
       <c r="R30" s="18" t="n"/>
       <c r="S30" s="18" t="n">
-        <v>0.5489475379859726</v>
+        <v>0.48273361872466</v>
       </c>
       <c r="T30" s="17" t="n">
         <v>1.129465748934775</v>
@@ -12809,7 +12809,7 @@
       <c r="Q31" s="18" t="n"/>
       <c r="R31" s="18" t="n"/>
       <c r="S31" s="18" t="n">
-        <v>0.6874798744570032</v>
+        <v>0.6164276829751248</v>
       </c>
       <c r="T31" s="17" t="n">
         <v>2.232172470978441</v>
@@ -12999,7 +12999,7 @@
       <c r="Q33" s="18" t="n"/>
       <c r="R33" s="18" t="n"/>
       <c r="S33" s="18" t="n">
-        <v>0.5680562237521595</v>
+        <v>0.6488825946202985</v>
       </c>
       <c r="T33" s="17" t="n">
         <v>0.5992578849721706</v>
@@ -13081,9 +13081,9 @@
       <c r="M34" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N34" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N34" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O34" s="16" t="inlineStr">
@@ -13094,7 +13094,9 @@
       <c r="P34" s="17" t="n"/>
       <c r="Q34" s="18" t="n"/>
       <c r="R34" s="18" t="n"/>
-      <c r="S34" s="18" t="n"/>
+      <c r="S34" s="18" t="n">
+        <v>0.3479216171436539</v>
+      </c>
       <c r="T34" s="17" t="n">
         <v>0.8013483146067415</v>
       </c>
@@ -13189,7 +13191,7 @@
       <c r="Q35" s="18" t="n"/>
       <c r="R35" s="18" t="n"/>
       <c r="S35" s="18" t="n">
-        <v>0.5298086629929519</v>
+        <v>0.5516922261144585</v>
       </c>
       <c r="T35" s="17" t="n">
         <v>0.5971049457177324</v>
@@ -13285,7 +13287,7 @@
       <c r="Q36" s="18" t="n"/>
       <c r="R36" s="18" t="n"/>
       <c r="S36" s="18" t="n">
-        <v>0.4579627965972348</v>
+        <v>0.3885884492791233</v>
       </c>
       <c r="T36" s="17" t="n">
         <v>1.854568854568855</v>
@@ -13367,9 +13369,9 @@
       <c r="M37" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N37" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N37" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O37" s="16" t="inlineStr">
@@ -13380,7 +13382,9 @@
       <c r="P37" s="17" t="n"/>
       <c r="Q37" s="18" t="n"/>
       <c r="R37" s="18" t="n"/>
-      <c r="S37" s="18" t="n"/>
+      <c r="S37" s="18" t="n">
+        <v>0.3179014583720582</v>
+      </c>
       <c r="T37" s="17" t="n">
         <v>0.918032786885246</v>
       </c>
@@ -13461,9 +13465,9 @@
       <c r="M38" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N38" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N38" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O38" s="16" t="inlineStr">
@@ -13475,7 +13479,7 @@
       <c r="Q38" s="18" t="n"/>
       <c r="R38" s="18" t="n"/>
       <c r="S38" s="18" t="n">
-        <v>0.7087262728717952</v>
+        <v>0.6383737152365203</v>
       </c>
       <c r="T38" s="17" t="n">
         <v>0.7993943981831944</v>
@@ -13751,7 +13755,7 @@
       <c r="Q41" s="18" t="n"/>
       <c r="R41" s="18" t="n"/>
       <c r="S41" s="18" t="n">
-        <v>0.3493201231905405</v>
+        <v>0.3602608494594197</v>
       </c>
       <c r="T41" s="17" t="n">
         <v>0.8201233981964879</v>
@@ -13847,7 +13851,7 @@
       <c r="Q42" s="18" t="n"/>
       <c r="R42" s="18" t="n"/>
       <c r="S42" s="18" t="n">
-        <v>0.5185861677186915</v>
+        <v>0.5001515439224913</v>
       </c>
       <c r="T42" s="17" t="n">
         <v>0.8588977797813591</v>
@@ -13943,7 +13947,7 @@
       <c r="Q43" s="18" t="n"/>
       <c r="R43" s="18" t="n"/>
       <c r="S43" s="18" t="n">
-        <v>0.7897383614491162</v>
+        <v>0.7810968059819697</v>
       </c>
       <c r="T43" s="17" t="n">
         <v>0.5729337391711544</v>
@@ -14119,9 +14123,9 @@
       <c r="M45" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N45" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N45" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O45" s="16" t="inlineStr">
@@ -14132,7 +14136,9 @@
       <c r="P45" s="17" t="n"/>
       <c r="Q45" s="18" t="n"/>
       <c r="R45" s="18" t="n"/>
-      <c r="S45" s="18" t="n"/>
+      <c r="S45" s="18" t="n">
+        <v>0.460140872072592</v>
+      </c>
       <c r="T45" s="17" t="n">
         <v>1.280750137892995</v>
       </c>
@@ -14321,7 +14327,7 @@
       <c r="Q47" s="18" t="n"/>
       <c r="R47" s="18" t="n"/>
       <c r="S47" s="18" t="n">
-        <v>0.4486711006782491</v>
+        <v>0.4396916957463503</v>
       </c>
       <c r="T47" s="17" t="n">
         <v>0.4559999999999999</v>
@@ -14403,9 +14409,9 @@
       <c r="M48" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N48" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N48" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O48" s="16" t="inlineStr">
@@ -14417,7 +14423,7 @@
       <c r="Q48" s="18" t="n"/>
       <c r="R48" s="18" t="n"/>
       <c r="S48" s="18" t="n">
-        <v>0.6499942501733138</v>
+        <v>0.8207130606863607</v>
       </c>
       <c r="T48" s="17" t="n">
         <v>3.06290672451193</v>
@@ -14513,7 +14519,7 @@
       <c r="Q49" s="18" t="n"/>
       <c r="R49" s="18" t="n"/>
       <c r="S49" s="18" t="n">
-        <v>0.6864606144513272</v>
+        <v>0.6430711912021507</v>
       </c>
       <c r="T49" s="17" t="n">
         <v>1.116422513492675</v>
@@ -14609,7 +14615,7 @@
       <c r="Q50" s="18" t="n"/>
       <c r="R50" s="18" t="n"/>
       <c r="S50" s="18" t="n">
-        <v>0.3832366987160346</v>
+        <v>0.3709518559680663</v>
       </c>
       <c r="T50" s="17" t="n">
         <v>0.6371191135734073</v>
@@ -14705,7 +14711,7 @@
       <c r="Q51" s="18" t="n"/>
       <c r="R51" s="18" t="n"/>
       <c r="S51" s="18" t="n">
-        <v>0.7107489133768511</v>
+        <v>0.8091996947698779</v>
       </c>
       <c r="T51" s="17" t="n">
         <v>1.266488413547237</v>
@@ -14895,7 +14901,7 @@
       <c r="Q53" s="18" t="n"/>
       <c r="R53" s="18" t="n"/>
       <c r="S53" s="18" t="n">
-        <v>0.8380549899558498</v>
+        <v>0.8402116178044428</v>
       </c>
       <c r="T53" s="17" t="n">
         <v>0.5861386138613862</v>
@@ -14991,7 +14997,7 @@
       <c r="Q54" s="18" t="n"/>
       <c r="R54" s="18" t="n"/>
       <c r="S54" s="18" t="n">
-        <v>0.70127890276442</v>
+        <v>0.7195458722834124</v>
       </c>
       <c r="T54" s="17" t="n">
         <v>0.423160173160173</v>
@@ -15087,7 +15093,7 @@
       <c r="Q55" s="18" t="n"/>
       <c r="R55" s="18" t="n"/>
       <c r="S55" s="18" t="n">
-        <v>0.6359166147168913</v>
+        <v>0.5599731114578178</v>
       </c>
       <c r="T55" s="17" t="n">
         <v>0.43733153638814</v>
@@ -15169,9 +15175,9 @@
       <c r="M56" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N56" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N56" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O56" s="16" t="inlineStr">
@@ -15183,7 +15189,7 @@
       <c r="Q56" s="18" t="n"/>
       <c r="R56" s="18" t="n"/>
       <c r="S56" s="18" t="n">
-        <v>0.7089553123233314</v>
+        <v>0.6690339461096686</v>
       </c>
       <c r="T56" s="17" t="n">
         <v>0.700486448922863</v>
@@ -15279,7 +15285,7 @@
       <c r="Q57" s="18" t="n"/>
       <c r="R57" s="18" t="n"/>
       <c r="S57" s="18" t="n">
-        <v>0.5251063900850369</v>
+        <v>0.4749133011867396</v>
       </c>
       <c r="T57" s="17" t="n">
         <v>0.5272340425531916</v>
@@ -15375,7 +15381,7 @@
       <c r="Q58" s="18" t="n"/>
       <c r="R58" s="18" t="n"/>
       <c r="S58" s="18" t="n">
-        <v>0.2602566029072812</v>
+        <v>0.1546277792513661</v>
       </c>
       <c r="T58" s="17" t="n">
         <v>1.593871595330739</v>
@@ -15565,7 +15571,7 @@
       <c r="Q60" s="18" t="n"/>
       <c r="R60" s="18" t="n"/>
       <c r="S60" s="18" t="n">
-        <v>0.5751183088804795</v>
+        <v>0.5179287585060368</v>
       </c>
       <c r="T60" s="17" t="n">
         <v>0.6898263027295284</v>
@@ -15661,7 +15667,7 @@
       <c r="Q61" s="18" t="n"/>
       <c r="R61" s="18" t="n"/>
       <c r="S61" s="18" t="n">
-        <v>0.5873113541283496</v>
+        <v>0.3144685659740958</v>
       </c>
       <c r="T61" s="17" t="n">
         <v>0.7827248441674086</v>
@@ -15753,7 +15759,7 @@
       <c r="Q62" s="18" t="n"/>
       <c r="R62" s="18" t="n"/>
       <c r="S62" s="18" t="n">
-        <v>0.4644701407156103</v>
+        <v>0.4528000208854522</v>
       </c>
       <c r="T62" s="17" t="n">
         <v>0.5521739130434784</v>
@@ -15849,7 +15855,7 @@
       <c r="Q63" s="18" t="n"/>
       <c r="R63" s="18" t="n"/>
       <c r="S63" s="18" t="n">
-        <v>0.7390827440060777</v>
+        <v>0.7391739146520225</v>
       </c>
       <c r="T63" s="17" t="n">
         <v>0.5376696303228825</v>
@@ -15945,7 +15951,7 @@
       <c r="Q64" s="18" t="n"/>
       <c r="R64" s="18" t="n"/>
       <c r="S64" s="18" t="n">
-        <v>0.3996871580391046</v>
+        <v>0.4505335429163548</v>
       </c>
       <c r="T64" s="17" t="n">
         <v>0.8261376896149359</v>
@@ -16131,7 +16137,7 @@
       <c r="Q66" s="18" t="n"/>
       <c r="R66" s="18" t="n"/>
       <c r="S66" s="18" t="n">
-        <v>0.4485279789269557</v>
+        <v>0.6359324328828446</v>
       </c>
       <c r="T66" s="17" t="n">
         <v>0.4685191698909603</v>
@@ -16213,9 +16219,9 @@
       <c r="M67" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N67" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N67" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O67" s="16" t="inlineStr">
@@ -16227,7 +16233,7 @@
       <c r="Q67" s="18" t="n"/>
       <c r="R67" s="18" t="n"/>
       <c r="S67" s="18" t="n">
-        <v>0.5721992649149387</v>
+        <v>0.7112214091586997</v>
       </c>
       <c r="T67" s="17" t="n">
         <v>1.049306625577812</v>
@@ -16323,7 +16329,7 @@
       <c r="Q68" s="18" t="n"/>
       <c r="R68" s="18" t="n"/>
       <c r="S68" s="18" t="n">
-        <v>0.341223904818644</v>
+        <v>0.4679357761128102</v>
       </c>
       <c r="T68" s="17" t="n">
         <v>0.4529217627645119</v>
@@ -16607,7 +16613,7 @@
       <c r="Q71" s="18" t="n"/>
       <c r="R71" s="18" t="n"/>
       <c r="S71" s="18" t="n">
-        <v>0.4006195882175567</v>
+        <v>0.5563691861057682</v>
       </c>
       <c r="T71" s="17" t="n">
         <v>0.6445047489823608</v>
@@ -16703,7 +16709,7 @@
       <c r="Q72" s="18" t="n"/>
       <c r="R72" s="18" t="n"/>
       <c r="S72" s="18" t="n">
-        <v>0.8159473846553051</v>
+        <v>0.8048734007659614</v>
       </c>
       <c r="T72" s="17" t="n">
         <v>1.160136286201022</v>
@@ -16799,7 +16805,7 @@
       <c r="Q73" s="18" t="n"/>
       <c r="R73" s="18" t="n"/>
       <c r="S73" s="18" t="n">
-        <v>0.367917833091275</v>
+        <v>0.5350119024669122</v>
       </c>
       <c r="T73" s="17" t="n">
         <v>0.8682745825602971</v>
@@ -17083,7 +17089,7 @@
       <c r="Q76" s="18" t="n"/>
       <c r="R76" s="18" t="n"/>
       <c r="S76" s="18" t="n">
-        <v>0.2738600116562628</v>
+        <v>0.2820060101901576</v>
       </c>
       <c r="T76" s="17" t="n">
         <v>0.8571834992887626</v>
@@ -17165,9 +17171,9 @@
       <c r="M77" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N77" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N77" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O77" s="16" t="inlineStr">
@@ -17179,7 +17185,7 @@
       <c r="Q77" s="18" t="n"/>
       <c r="R77" s="18" t="n"/>
       <c r="S77" s="18" t="n">
-        <v>0.6746286573561653</v>
+        <v>0.756322091248415</v>
       </c>
       <c r="T77" s="17" t="n">
         <v>1.130935251798561</v>
@@ -17275,7 +17281,7 @@
       <c r="Q78" s="18" t="n"/>
       <c r="R78" s="18" t="n"/>
       <c r="S78" s="18" t="n">
-        <v>0.4359681587812185</v>
+        <v>0.412536660645403</v>
       </c>
       <c r="T78" s="17" t="n">
         <v>0.6416131989000917</v>
@@ -17451,9 +17457,9 @@
       <c r="M80" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N80" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N80" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O80" s="16" t="inlineStr">
@@ -17464,7 +17470,9 @@
       <c r="P80" s="17" t="n"/>
       <c r="Q80" s="18" t="n"/>
       <c r="R80" s="18" t="n"/>
-      <c r="S80" s="18" t="n"/>
+      <c r="S80" s="18" t="n">
+        <v>0.5539922794159842</v>
+      </c>
       <c r="T80" s="17" t="n">
         <v>0.4933774834437086</v>
       </c>
@@ -17559,7 +17567,7 @@
       <c r="Q81" s="18" t="n"/>
       <c r="R81" s="18" t="n"/>
       <c r="S81" s="18" t="n">
-        <v>0.5845577479744137</v>
+        <v>0.551363436926618</v>
       </c>
       <c r="T81" s="17" t="n">
         <v>0.420997375328084</v>
@@ -17735,9 +17743,9 @@
       <c r="M83" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N83" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N83" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O83" s="16" t="inlineStr">
@@ -17755,7 +17763,7 @@
         <v>0.8584378</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>0.7040862588423586</v>
+        <v>0.6292848239662183</v>
       </c>
       <c r="T83" s="17" t="n">
         <v>0.4898828541001063</v>
@@ -17837,9 +17845,9 @@
       <c r="M84" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N84" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N84" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O84" s="16" t="inlineStr">
@@ -17851,7 +17859,7 @@
       <c r="Q84" s="18" t="n"/>
       <c r="R84" s="18" t="n"/>
       <c r="S84" s="18" t="n">
-        <v>0.6053347250509514</v>
+        <v>0.7228236767824699</v>
       </c>
       <c r="T84" s="17" t="n">
         <v>0.7576736672051696</v>
@@ -17947,7 +17955,7 @@
       <c r="Q85" s="18" t="n"/>
       <c r="R85" s="18" t="n"/>
       <c r="S85" s="18" t="n">
-        <v>0.6830194087786177</v>
+        <v>0.6141862423499979</v>
       </c>
       <c r="T85" s="17" t="n">
         <v>0.8475120385232744</v>
@@ -18141,7 +18149,7 @@
         <v>0.5799241000000001</v>
       </c>
       <c r="S87" s="18" t="n">
-        <v>0.6676996543323822</v>
+        <v>0.5926137051415603</v>
       </c>
       <c r="T87" s="17" t="n">
         <v>0.241304347826087</v>
@@ -18239,7 +18247,7 @@
         <v>0.6444306400000001</v>
       </c>
       <c r="S88" s="18" t="n">
-        <v>0.6796658361637711</v>
+        <v>0.6048916853842751</v>
       </c>
       <c r="T88" s="17" t="n">
         <v>0.5049288061336252</v>
@@ -18337,7 +18345,7 @@
         <v>0.6621961</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>0.3989554176223963</v>
+        <v>0.3661934795337199</v>
       </c>
       <c r="T89" s="17" t="n">
         <v>0.3539166484835261</v>
@@ -18531,7 +18539,7 @@
         <v>0.797227</v>
       </c>
       <c r="S91" s="18" t="n">
-        <v>0.5875457884006819</v>
+        <v>0.535974950519122</v>
       </c>
       <c r="T91" s="17" t="n">
         <v>0.1350762527233115</v>
@@ -18629,7 +18637,7 @@
         <v>0.7015838599999999</v>
       </c>
       <c r="S92" s="18" t="n">
-        <v>0.6160623490367652</v>
+        <v>0.688482655294375</v>
       </c>
       <c r="T92" s="17" t="n">
         <v>0.6242441693060754</v>
@@ -18723,7 +18731,7 @@
         <v>0.5952269</v>
       </c>
       <c r="S93" s="18" t="n">
-        <v>0.8885781020284487</v>
+        <v>0.8140032972729476</v>
       </c>
       <c r="T93" s="17" t="n">
         <v>0.101354644042034</v>
@@ -18801,9 +18809,9 @@
       <c r="M94" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N94" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N94" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O94" s="14" t="inlineStr">
@@ -18820,9 +18828,7 @@
       <c r="R94" s="18" t="n">
         <v>0.4740045</v>
       </c>
-      <c r="S94" s="18" t="n">
-        <v>0.4848414353262132</v>
-      </c>
+      <c r="S94" s="18" t="n"/>
       <c r="T94" s="17" t="n">
         <v>0.07910014513788099</v>
       </c>
@@ -18919,7 +18925,7 @@
         <v>0.7533674</v>
       </c>
       <c r="S95" s="18" t="n">
-        <v>0.4718390368796714</v>
+        <v>0.518144016234189</v>
       </c>
       <c r="T95" s="17" t="n">
         <v>0.2254495159059473</v>
@@ -19109,7 +19115,7 @@
         <v>0.6124555</v>
       </c>
       <c r="S97" s="18" t="n">
-        <v>0.7976370096510477</v>
+        <v>0.8085260642844823</v>
       </c>
       <c r="T97" s="17" t="n">
         <v>0.6250829462508294</v>
@@ -19187,9 +19193,9 @@
       <c r="M98" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N98" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N98" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O98" s="14" t="inlineStr">
@@ -19207,7 +19213,7 @@
         <v>0.61080986</v>
       </c>
       <c r="S98" s="18" t="n">
-        <v>0.7558045131122967</v>
+        <v>0.6807571589528316</v>
       </c>
       <c r="T98" s="17" t="n">
         <v>0.1275347906978474</v>
@@ -19305,7 +19311,7 @@
         <v>0.7564476</v>
       </c>
       <c r="S99" s="18" t="n">
-        <v>0.5711350152478117</v>
+        <v>0.5485995842160901</v>
       </c>
       <c r="T99" s="17" t="n">
         <v>0.0517879161528975</v>
@@ -19403,7 +19409,7 @@
         <v>0.56387496</v>
       </c>
       <c r="S100" s="18" t="n">
-        <v>0.7502364967242765</v>
+        <v>0.7367224356129094</v>
       </c>
       <c r="T100" s="17" t="n">
         <v>0.0948739733786461</v>
@@ -19501,7 +19507,7 @@
         <v>0.6822511</v>
       </c>
       <c r="S101" s="18" t="n">
-        <v>0.4299702005749749</v>
+        <v>0.4422383878890418</v>
       </c>
       <c r="T101" s="17" t="n">
         <v>0.2528548123980423</v>
@@ -19599,7 +19605,7 @@
         <v>0.6793217</v>
       </c>
       <c r="S102" s="18" t="n">
-        <v>0.4588315163397575</v>
+        <v>0.5639077740296889</v>
       </c>
       <c r="T102" s="17" t="n">
         <v>0.1750380517503804</v>
@@ -19793,7 +19799,7 @@
         <v>0.74681824</v>
       </c>
       <c r="S104" s="18" t="n">
-        <v>0.4795695804731336</v>
+        <v>0.4193456708209295</v>
       </c>
       <c r="T104" s="17" t="n">
         <v>0.0638888888888888</v>
@@ -19891,7 +19897,7 @@
         <v>0.6028521</v>
       </c>
       <c r="S105" s="18" t="n">
-        <v>0.438818614812509</v>
+        <v>0.6076325708818344</v>
       </c>
       <c r="T105" s="17" t="n">
         <v>0.1814427312775328</v>
@@ -19989,7 +19995,7 @@
         <v>0.6762183</v>
       </c>
       <c r="S106" s="18" t="n">
-        <v>0.5534259509093322</v>
+        <v>0.5372392767356612</v>
       </c>
       <c r="T106" s="17" t="n">
         <v>0.2920696324951644</v>
@@ -20183,7 +20189,7 @@
         <v>0.7141791</v>
       </c>
       <c r="S108" s="18" t="n">
-        <v>0.4292392536541854</v>
+        <v>0.4636421683408946</v>
       </c>
       <c r="T108" s="17" t="n">
         <v>0.0620155038759691</v>
@@ -20377,7 +20383,7 @@
         <v>0.7460955</v>
       </c>
       <c r="S110" s="18" t="n">
-        <v>0.5818403788343574</v>
+        <v>0.5526622201382977</v>
       </c>
       <c r="T110" s="17" t="n">
         <v>0.0607210626185958</v>
@@ -20475,7 +20481,7 @@
         <v>0.5294514299999999</v>
       </c>
       <c r="S111" s="18" t="n">
-        <v>0.4690888072828217</v>
+        <v>0.4211248688274214</v>
       </c>
       <c r="T111" s="17" t="n">
         <v>0.1102299762093577</v>
@@ -20669,7 +20675,7 @@
         <v>0.7541239</v>
       </c>
       <c r="S113" s="18" t="n">
-        <v>0.7631829238198193</v>
+        <v>0.7316986378535655</v>
       </c>
       <c r="T113" s="17" t="n">
         <v>0.4902470741222366</v>
@@ -20767,7 +20773,7 @@
         <v>0.41235414</v>
       </c>
       <c r="S114" s="18" t="n">
-        <v>0.4887519344129748</v>
+        <v>0.5579900398150531</v>
       </c>
       <c r="T114" s="17" t="n">
         <v>0.1542288557213931</v>
@@ -20941,9 +20947,9 @@
       <c r="M116" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N116" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N116" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="O116" s="14" t="inlineStr">
@@ -20960,7 +20966,9 @@
       <c r="R116" s="18" t="n">
         <v>0.6918013</v>
       </c>
-      <c r="S116" s="18" t="n"/>
+      <c r="S116" s="18" t="n">
+        <v>0.2280024160839999</v>
+      </c>
       <c r="T116" s="17" t="n">
         <v>0.1101321585903083</v>
       </c>
@@ -21057,7 +21065,7 @@
         <v>0.5379344</v>
       </c>
       <c r="S117" s="18" t="n">
-        <v>0.4535132066046265</v>
+        <v>0.4103206188604699</v>
       </c>
       <c r="T117" s="17" t="n">
         <v>0.1344262295081968</v>
@@ -21251,7 +21259,7 @@
         <v>0.7688339</v>
       </c>
       <c r="S119" s="18" t="n">
-        <v>0.3859625272043039</v>
+        <v>0.6898914812114286</v>
       </c>
       <c r="T119" s="17" t="n">
         <v>0.4004282655246254</v>
@@ -21329,9 +21337,9 @@
       <c r="M120" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N120" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N120" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O120" s="14" t="inlineStr">
@@ -21349,7 +21357,7 @@
         <v>0.47521228</v>
       </c>
       <c r="S120" s="18" t="n">
-        <v>0.7661122173600291</v>
+        <v>0.5725044106687289</v>
       </c>
       <c r="T120" s="17" t="n">
         <v>0.0562770562770562</v>
@@ -21447,7 +21455,7 @@
         <v>0.6450075</v>
       </c>
       <c r="S121" s="18" t="n">
-        <v>0.3997487563641301</v>
+        <v>0.4023755936158622</v>
       </c>
       <c r="T121" s="17" t="n">
         <v>0.1084507042253521</v>
@@ -21545,7 +21553,7 @@
         <v>0.61368763</v>
       </c>
       <c r="S122" s="18" t="n">
-        <v>0.6311896398461916</v>
+        <v>0.653626963695162</v>
       </c>
       <c r="T122" s="17" t="n">
         <v>0.2126503686457121</v>
@@ -21643,7 +21651,7 @@
         <v>0.42972246</v>
       </c>
       <c r="S123" s="18" t="n">
-        <v>0.4986473312845691</v>
+        <v>0.4495665866880915</v>
       </c>
       <c r="T123" s="17" t="n">
         <v>0.07599517490952951</v>
@@ -21737,7 +21745,7 @@
         <v>0.6199526</v>
       </c>
       <c r="S124" s="18" t="n">
-        <v>0.7106811549672576</v>
+        <v>0.7983754112381793</v>
       </c>
       <c r="T124" s="17" t="n">
         <v>0.4006554690700532</v>
@@ -21835,7 +21843,7 @@
         <v>0.6540404</v>
       </c>
       <c r="S125" s="18" t="n">
-        <v>0.6920142031893026</v>
+        <v>0.6466904873140894</v>
       </c>
       <c r="T125" s="17" t="n">
         <v>0.1001150747986192</v>
@@ -21933,7 +21941,7 @@
         <v>0.7648357</v>
       </c>
       <c r="S126" s="18" t="n">
-        <v>0.6975453013847832</v>
+        <v>0.4943936221120616</v>
       </c>
       <c r="T126" s="17" t="n">
         <v>0.0897397547113372</v>
@@ -22031,7 +22039,7 @@
         <v>0.6251069</v>
       </c>
       <c r="S127" s="18" t="n">
-        <v>0.628616613718014</v>
+        <v>0.5681245270008837</v>
       </c>
       <c r="T127" s="17" t="n">
         <v>0.3151714419915454</v>
@@ -22321,7 +22329,7 @@
         <v>0.7136941</v>
       </c>
       <c r="S130" s="18" t="n">
-        <v>0.4944135775064397</v>
+        <v>0.5367135231706677</v>
       </c>
       <c r="T130" s="17" t="n">
         <v>0.0499776885319054</v>
@@ -22419,7 +22427,7 @@
         <v>0.6370595999999999</v>
       </c>
       <c r="S131" s="18" t="n">
-        <v>0.7220756226803104</v>
+        <v>0.7628343995670682</v>
       </c>
       <c r="T131" s="17" t="n">
         <v>0.2557510148849797</v>
@@ -22513,7 +22521,7 @@
         <v>0.66082424</v>
       </c>
       <c r="S132" s="18" t="n">
-        <v>0.8277770435166829</v>
+        <v>0.8325099895189975</v>
       </c>
       <c r="T132" s="17" t="n">
         <v>0.29073856975381</v>
@@ -22611,7 +22619,7 @@
         <v>0.5493093999999999</v>
       </c>
       <c r="S133" s="18" t="n">
-        <v>0.6954552303129671</v>
+        <v>0.6572581444411216</v>
       </c>
       <c r="T133" s="17" t="n">
         <v>0.3137254901960784</v>
@@ -22705,7 +22713,7 @@
         <v>0.50447184</v>
       </c>
       <c r="S134" s="18" t="n">
-        <v>0.5099532171938823</v>
+        <v>0.5381288311867291</v>
       </c>
       <c r="T134" s="17" t="n">
         <v>0.3819397993311038</v>
@@ -22799,7 +22807,7 @@
         <v>0.44490305</v>
       </c>
       <c r="S135" s="18" t="n">
-        <v>0.3877382370973756</v>
+        <v>0.3599623466811488</v>
       </c>
       <c r="T135" s="17" t="n">
         <v>0.0124378109452738</v>
@@ -22897,7 +22905,7 @@
         <v>0.52244896</v>
       </c>
       <c r="S136" s="18" t="n">
-        <v>0.637919664184141</v>
+        <v>0.6781445298670458</v>
       </c>
       <c r="T136" s="17" t="n">
         <v>0.1412429378531072</v>
@@ -23259,9 +23267,9 @@
       <c r="M140" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N140" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N140" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O140" s="21" t="inlineStr">
@@ -23278,7 +23286,9 @@
       <c r="R140" s="18" t="n">
         <v>0.5899036</v>
       </c>
-      <c r="S140" s="18" t="n"/>
+      <c r="S140" s="18" t="n">
+        <v>0.6282508196700228</v>
+      </c>
       <c r="T140" s="17" t="n">
         <v>0.1924715909090908</v>
       </c>
@@ -23471,7 +23481,7 @@
         <v>0.5174432</v>
       </c>
       <c r="S142" s="18" t="n">
-        <v>0.5967063482325993</v>
+        <v>0.6112279217681167</v>
       </c>
       <c r="T142" s="17" t="n">
         <v>0.1481716339040371</v>
@@ -23569,7 +23579,7 @@
         <v>0.42647213</v>
       </c>
       <c r="S143" s="18" t="n">
-        <v>0.4623198406024389</v>
+        <v>0.3827946807111425</v>
       </c>
       <c r="T143" s="17" t="n">
         <v>0.0774100719424459</v>
@@ -23663,7 +23673,7 @@
         <v>0.509744</v>
       </c>
       <c r="S144" s="18" t="n">
-        <v>0.2564519457368456</v>
+        <v>0.2256703905824698</v>
       </c>
       <c r="T144" s="17" t="n">
         <v>0.09498401001112319</v>
@@ -23857,7 +23867,7 @@
         <v>0.40104166</v>
       </c>
       <c r="S146" s="18" t="n">
-        <v>0.4042994839997469</v>
+        <v>0.4661451046809245</v>
       </c>
       <c r="T146" s="17" t="n">
         <v>0.3895538628944506</v>
@@ -23935,9 +23945,9 @@
       <c r="M147" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N147" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N147" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O147" s="21" t="inlineStr">
@@ -23955,7 +23965,7 @@
         <v>0.5080917</v>
       </c>
       <c r="S147" s="18" t="n">
-        <v>0.39617430626733</v>
+        <v>0.7478920099090776</v>
       </c>
       <c r="T147" s="17" t="n">
         <v>0.7192353643966549</v>
@@ -24033,9 +24043,9 @@
       <c r="M148" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N148" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N148" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O148" s="16" t="inlineStr">
@@ -24052,7 +24062,9 @@
       <c r="R148" s="18" t="n">
         <v>0.524483</v>
       </c>
-      <c r="S148" s="18" t="n"/>
+      <c r="S148" s="18" t="n">
+        <v>0.3546324037987675</v>
+      </c>
       <c r="T148" s="17" t="n">
         <v>0.5098736176935228</v>
       </c>
@@ -24149,7 +24161,7 @@
         <v>0.5018835</v>
       </c>
       <c r="S149" s="18" t="n">
-        <v>0.5003909894011075</v>
+        <v>0.3321650509599927</v>
       </c>
       <c r="T149" s="17" t="n">
         <v>0.0521091811414391</v>
@@ -24227,9 +24239,9 @@
       <c r="M150" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N150" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N150" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O150" s="21" t="inlineStr">
@@ -24247,7 +24259,7 @@
         <v>0.5474571</v>
       </c>
       <c r="S150" s="18" t="n">
-        <v>0.7081222675629875</v>
+        <v>0.6821026934293438</v>
       </c>
       <c r="T150" s="17" t="n">
         <v>1.239852398523985</v>
@@ -24511,9 +24523,9 @@
       <c r="M153" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N153" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N153" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O153" s="21" t="inlineStr">
@@ -24530,9 +24542,7 @@
       <c r="R153" s="18" t="n">
         <v>0.61507833</v>
       </c>
-      <c r="S153" s="18" t="n">
-        <v>0.5151298210251416</v>
-      </c>
+      <c r="S153" s="18" t="n"/>
       <c r="T153" s="17" t="n">
         <v>0.4707903780068729</v>
       </c>
@@ -24725,7 +24735,7 @@
         <v>0.6898404</v>
       </c>
       <c r="S155" s="18" t="n">
-        <v>0.6118023213840291</v>
+        <v>0.6637153941830167</v>
       </c>
       <c r="T155" s="17" t="n">
         <v>0.215880893300248</v>
@@ -24803,9 +24813,9 @@
       <c r="M156" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N156" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N156" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O156" s="21" t="inlineStr">
@@ -24823,7 +24833,7 @@
         <v>0.40243122</v>
       </c>
       <c r="S156" s="18" t="n">
-        <v>0.7142043783722865</v>
+        <v>0.6449897202305286</v>
       </c>
       <c r="T156" s="17" t="n">
         <v>0.0973724884080371</v>
@@ -24921,7 +24931,7 @@
         <v>0.6350739</v>
       </c>
       <c r="S157" s="18" t="n">
-        <v>0.6373911084086824</v>
+        <v>0.5783273893211477</v>
       </c>
       <c r="T157" s="17" t="n">
         <v>0.2024720423778694</v>
@@ -25019,7 +25029,7 @@
         <v>0.677433</v>
       </c>
       <c r="S158" s="18" t="n">
-        <v>0.5631813412070065</v>
+        <v>0.5652489544729457</v>
       </c>
       <c r="T158" s="17" t="n">
         <v>0.4381315966763981</v>
@@ -25117,7 +25127,7 @@
         <v>0.50525796</v>
       </c>
       <c r="S159" s="18" t="n">
-        <v>0.3920009246740148</v>
+        <v>0.38525283713742</v>
       </c>
       <c r="T159" s="17" t="n">
         <v>0.1983695652173913</v>
@@ -25311,7 +25321,7 @@
         <v>0.3169572</v>
       </c>
       <c r="S161" s="18" t="n">
-        <v>0.5895925564673956</v>
+        <v>0.5504117210258869</v>
       </c>
       <c r="T161" s="17" t="n">
         <v>0.0643642072213501</v>
@@ -25505,7 +25515,7 @@
         <v>0.79817116</v>
       </c>
       <c r="S163" s="18" t="n">
-        <v>0.3764337569875877</v>
+        <v>0.3463349209490567</v>
       </c>
       <c r="T163" s="17" t="n">
         <v>0.645628556647698</v>
@@ -25695,7 +25705,7 @@
         <v>0.4359606</v>
       </c>
       <c r="S165" s="18" t="n">
-        <v>0.6342326442947561</v>
+        <v>0.5923361430655831</v>
       </c>
       <c r="T165" s="17" t="n">
         <v>0.0254691689008044</v>
@@ -25793,7 +25803,7 @@
         <v>0.59117407</v>
       </c>
       <c r="S166" s="18" t="n">
-        <v>0.4975979622564719</v>
+        <v>0.4726772964345742</v>
       </c>
       <c r="T166" s="17" t="n">
         <v>0.2673644148430067</v>
@@ -25891,7 +25901,7 @@
         <v>0.7674044</v>
       </c>
       <c r="S167" s="18" t="n">
-        <v>0.6853504432986548</v>
+        <v>0.6494019226643806</v>
       </c>
       <c r="T167" s="17" t="n">
         <v>1.235034887991186</v>
@@ -26085,7 +26095,7 @@
         <v>0.6155898</v>
       </c>
       <c r="S169" s="18" t="n">
-        <v>0.2414145710297299</v>
+        <v>0.2269373693530962</v>
       </c>
       <c r="T169" s="17" t="n">
         <v>0.2875894988066823</v>
@@ -26375,7 +26385,7 @@
         <v>0.79823714</v>
       </c>
       <c r="S172" s="18" t="n">
-        <v>0.6819943733525524</v>
+        <v>0.4593352737690911</v>
       </c>
       <c r="T172" s="17" t="n">
         <v>0.168091168091168</v>
@@ -26473,7 +26483,7 @@
         <v>0.78232545</v>
       </c>
       <c r="S173" s="18" t="n">
-        <v>0.3809024451735009</v>
+        <v>0.3627747816020117</v>
       </c>
       <c r="T173" s="17" t="n">
         <v>0.7284583139264089</v>
@@ -26763,7 +26773,7 @@
         <v>0.56830347</v>
       </c>
       <c r="S176" s="18" t="n">
-        <v>0.6015444384280689</v>
+        <v>0.5350897949622525</v>
       </c>
       <c r="T176" s="17" t="n">
         <v>0.5705777248362123</v>
@@ -26861,7 +26871,7 @@
         <v>0.6730504</v>
       </c>
       <c r="S177" s="18" t="n">
-        <v>0.7249728302897493</v>
+        <v>0.704864522730243</v>
       </c>
       <c r="T177" s="17" t="n">
         <v>0.6636288318144157</v>
@@ -27055,7 +27065,7 @@
         <v>0.6290615000000001</v>
       </c>
       <c r="S179" s="18" t="n">
-        <v>0.5217851237281956</v>
+        <v>0.6086001759799051</v>
       </c>
       <c r="T179" s="17" t="n">
         <v>1.681971227425773</v>
@@ -27249,7 +27259,7 @@
         <v>0.48124543</v>
       </c>
       <c r="S181" s="18" t="n">
-        <v>0.4639939577492211</v>
+        <v>0.5475721110246177</v>
       </c>
       <c r="T181" s="17" t="n">
         <v>0.3007273639327816</v>
@@ -27347,7 +27357,7 @@
         <v>0.39191207</v>
       </c>
       <c r="S182" s="18" t="n">
-        <v>0.4989662563364677</v>
+        <v>0.4472556757441553</v>
       </c>
       <c r="T182" s="17" t="n">
         <v>0.8547734627831716</v>
@@ -27541,7 +27551,7 @@
         <v>0.6417168</v>
       </c>
       <c r="S184" s="18" t="n">
-        <v>0.6111957223450711</v>
+        <v>0.613347550132328</v>
       </c>
       <c r="T184" s="17" t="n">
         <v>0.2914746543778803</v>
@@ -27639,7 +27649,7 @@
         <v>0.662113</v>
       </c>
       <c r="S185" s="18" t="n">
-        <v>0.5798110185003442</v>
+        <v>0.3989018748758752</v>
       </c>
       <c r="T185" s="17" t="n">
         <v>0.517126148705096</v>
@@ -27737,7 +27747,7 @@
         <v>0.458005</v>
       </c>
       <c r="S186" s="18" t="n">
-        <v>0.5075895024491962</v>
+        <v>0.4870951934408768</v>
       </c>
       <c r="T186" s="17" t="n">
         <v>0.2553407934893186</v>
@@ -27835,7 +27845,7 @@
         <v>0.5319593500000001</v>
       </c>
       <c r="S187" s="18" t="n">
-        <v>0.4701367768579749</v>
+        <v>0.502640582445207</v>
       </c>
       <c r="T187" s="17" t="n">
         <v>0.4033646322378716</v>
@@ -28029,7 +28039,7 @@
         <v>0.5718801</v>
       </c>
       <c r="S189" s="18" t="n">
-        <v>0.7298154941952422</v>
+        <v>0.703719114778422</v>
       </c>
       <c r="T189" s="17" t="n">
         <v>1.326359832635983</v>
@@ -28583,9 +28593,9 @@
       <c r="M195" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N195" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N195" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O195" s="16" t="inlineStr">
@@ -28596,9 +28606,7 @@
       <c r="P195" s="17" t="n"/>
       <c r="Q195" s="18" t="n"/>
       <c r="R195" s="18" t="n"/>
-      <c r="S195" s="18" t="n">
-        <v>0.4188639032945368</v>
-      </c>
+      <c r="S195" s="18" t="n"/>
       <c r="T195" s="17" t="n">
         <v>1.370262390670554</v>
       </c>
@@ -28693,7 +28701,7 @@
       <c r="Q196" s="18" t="n"/>
       <c r="R196" s="18" t="n"/>
       <c r="S196" s="18" t="n">
-        <v>0.5465089414279862</v>
+        <v>0.5524328325365158</v>
       </c>
       <c r="T196" s="17" t="n">
         <v>2.309030864981582</v>
@@ -28883,7 +28891,7 @@
       <c r="Q198" s="18" t="n"/>
       <c r="R198" s="18" t="n"/>
       <c r="S198" s="18" t="n">
-        <v>0.5016616614952305</v>
+        <v>0.5694716867756517</v>
       </c>
       <c r="T198" s="17" t="n">
         <v>0.5836477987421382</v>
@@ -28979,7 +28987,7 @@
       <c r="Q199" s="18" t="n"/>
       <c r="R199" s="18" t="n"/>
       <c r="S199" s="18" t="n">
-        <v>0.400414470588519</v>
+        <v>0.3950134923977524</v>
       </c>
       <c r="T199" s="17" t="n">
         <v>0.6681922196796339</v>
@@ -29075,7 +29083,7 @@
       <c r="Q200" s="18" t="n"/>
       <c r="R200" s="18" t="n"/>
       <c r="S200" s="18" t="n">
-        <v>0.8171678429056572</v>
+        <v>0.8185356759568183</v>
       </c>
       <c r="T200" s="17" t="n">
         <v>1.383198231392778</v>
@@ -29171,7 +29179,7 @@
       <c r="Q201" s="18" t="n"/>
       <c r="R201" s="18" t="n"/>
       <c r="S201" s="18" t="n">
-        <v>0.7992992784251252</v>
+        <v>0.7672410243941462</v>
       </c>
       <c r="T201" s="17" t="n">
         <v>2.184563758389262</v>
@@ -29267,7 +29275,7 @@
       <c r="Q202" s="18" t="n"/>
       <c r="R202" s="18" t="n"/>
       <c r="S202" s="18" t="n">
-        <v>0.536385900410801</v>
+        <v>0.588083418880909</v>
       </c>
       <c r="T202" s="17" t="n">
         <v>0.6980584285973508</v>
@@ -29363,7 +29371,7 @@
       <c r="Q203" s="18" t="n"/>
       <c r="R203" s="18" t="n"/>
       <c r="S203" s="18" t="n">
-        <v>0.6686915136282898</v>
+        <v>0.658904129317354</v>
       </c>
       <c r="T203" s="17" t="n">
         <v>0.5345744680851063</v>
@@ -29459,7 +29467,7 @@
       <c r="Q204" s="18" t="n"/>
       <c r="R204" s="18" t="n"/>
       <c r="S204" s="18" t="n">
-        <v>0.6330470623236018</v>
+        <v>0.4999262353124099</v>
       </c>
       <c r="T204" s="17" t="n">
         <v>0.5752589884216941</v>
@@ -29555,7 +29563,7 @@
       <c r="Q205" s="18" t="n"/>
       <c r="R205" s="18" t="n"/>
       <c r="S205" s="18" t="n">
-        <v>0.8082727645819985</v>
+        <v>0.7784775376740607</v>
       </c>
       <c r="T205" s="17" t="n">
         <v>0.4216300940438873</v>
@@ -29651,7 +29659,7 @@
       <c r="Q206" s="18" t="n"/>
       <c r="R206" s="18" t="n"/>
       <c r="S206" s="18" t="n">
-        <v>0.7642944008107606</v>
+        <v>0.7654415198409918</v>
       </c>
       <c r="T206" s="17" t="n">
         <v>0.5794356397371472</v>
@@ -29747,7 +29755,7 @@
       <c r="Q207" s="18" t="n"/>
       <c r="R207" s="18" t="n"/>
       <c r="S207" s="18" t="n">
-        <v>0.6513599391657903</v>
+        <v>0.576189405185519</v>
       </c>
       <c r="T207" s="17" t="n">
         <v>1.457037911583366</v>
@@ -29829,9 +29837,9 @@
       <c r="M208" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N208" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N208" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O208" s="16" t="inlineStr">
@@ -29842,7 +29850,9 @@
       <c r="P208" s="17" t="n"/>
       <c r="Q208" s="18" t="n"/>
       <c r="R208" s="18" t="n"/>
-      <c r="S208" s="18" t="n"/>
+      <c r="S208" s="18" t="n">
+        <v>0.6990780077129441</v>
+      </c>
       <c r="T208" s="17" t="n">
         <v>2.313176895306859</v>
       </c>
@@ -29923,9 +29933,9 @@
       <c r="M209" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N209" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N209" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O209" s="21" t="inlineStr">
@@ -29937,7 +29947,7 @@
       <c r="Q209" s="18" t="n"/>
       <c r="R209" s="18" t="n"/>
       <c r="S209" s="18" t="n">
-        <v>0.6937150769915084</v>
+        <v>0.732799278284156</v>
       </c>
       <c r="T209" s="17" t="n">
         <v>0.5412474849094568</v>
@@ -30207,9 +30217,9 @@
       <c r="M212" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N212" s="13" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="N212" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O212" s="16" t="inlineStr">
@@ -30221,7 +30231,7 @@
       <c r="Q212" s="18" t="n"/>
       <c r="R212" s="18" t="n"/>
       <c r="S212" s="18" t="n">
-        <v>0.248305308698976</v>
+        <v>0.4096678120031132</v>
       </c>
       <c r="T212" s="17" t="n">
         <v>1.022686567164179</v>
@@ -30511,7 +30521,7 @@
         <v>0.9741041</v>
       </c>
       <c r="S215" s="18" t="n">
-        <v>0.5907094620913483</v>
+        <v>0.5370441995702613</v>
       </c>
       <c r="T215" s="17" t="n">
         <v>1.872233400402415</v>
@@ -30783,7 +30793,7 @@
       <c r="Q218" s="18" t="n"/>
       <c r="R218" s="18" t="n"/>
       <c r="S218" s="18" t="n">
-        <v>0.4752680089120765</v>
+        <v>0.6166343403489902</v>
       </c>
       <c r="T218" s="17" t="n">
         <v>2.087695133149678</v>
@@ -30875,7 +30885,7 @@
       <c r="Q219" s="18" t="n"/>
       <c r="R219" s="18" t="n"/>
       <c r="S219" s="18" t="n">
-        <v>0.5606057475183241</v>
+        <v>0.500350907494957</v>
       </c>
       <c r="T219" s="17" t="n">
         <v>4.147182506307821</v>
@@ -30953,9 +30963,9 @@
       <c r="M220" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N220" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N220" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O220" s="16" t="inlineStr">
@@ -30967,7 +30977,7 @@
       <c r="Q220" s="18" t="n"/>
       <c r="R220" s="18" t="n"/>
       <c r="S220" s="18" t="n">
-        <v>0.6970809423869098</v>
+        <v>0.7446340637006647</v>
       </c>
       <c r="T220" s="17" t="n">
         <v>1.17151379567487</v>
@@ -31419,7 +31429,7 @@
       <c r="Q225" s="18" t="n"/>
       <c r="R225" s="18" t="n"/>
       <c r="S225" s="18" t="n">
-        <v>0.6344950715048612</v>
+        <v>0.5924610793154764</v>
       </c>
       <c r="T225" s="17" t="n">
         <v>5.118729096989966</v>
@@ -31511,7 +31521,7 @@
       <c r="Q226" s="18" t="n"/>
       <c r="R226" s="18" t="n"/>
       <c r="S226" s="18" t="n">
-        <v>0.375199286508996</v>
+        <v>0.3632669006718825</v>
       </c>
       <c r="T226" s="17" t="n">
         <v>2.216831948539265</v>
@@ -31603,7 +31613,7 @@
       <c r="Q227" s="18" t="n"/>
       <c r="R227" s="18" t="n"/>
       <c r="S227" s="18" t="n">
-        <v>0.7089632940509406</v>
+        <v>0.715393650655873</v>
       </c>
       <c r="T227" s="17" t="n">
         <v>4.571955719557195</v>
@@ -31785,7 +31795,7 @@
       <c r="Q229" s="18" t="n"/>
       <c r="R229" s="18" t="n"/>
       <c r="S229" s="18" t="n">
-        <v>0.4461580680859201</v>
+        <v>0.4630589526522282</v>
       </c>
       <c r="T229" s="17" t="n">
         <v>1.52037845705968</v>
@@ -31877,7 +31887,7 @@
       <c r="Q230" s="18" t="n"/>
       <c r="R230" s="18" t="n"/>
       <c r="S230" s="18" t="n">
-        <v>0.6130998075458268</v>
+        <v>0.5398159184689169</v>
       </c>
       <c r="T230" s="17" t="n">
         <v>2.994147843942505</v>
@@ -32055,7 +32065,7 @@
       <c r="Q232" s="18" t="n"/>
       <c r="R232" s="18" t="n"/>
       <c r="S232" s="18" t="n">
-        <v>0.5563806657559942</v>
+        <v>0.4320254899602103</v>
       </c>
       <c r="T232" s="17" t="n">
         <v>1.830379746835443</v>
@@ -32223,9 +32233,9 @@
       <c r="M234" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N234" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N234" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O234" s="16" t="inlineStr">
@@ -32237,7 +32247,7 @@
       <c r="Q234" s="18" t="n"/>
       <c r="R234" s="18" t="n"/>
       <c r="S234" s="18" t="n">
-        <v>0.6926488034332223</v>
+        <v>0.739914033986082</v>
       </c>
       <c r="T234" s="17" t="n">
         <v>1.856031128404669</v>
@@ -32329,7 +32339,7 @@
       <c r="Q235" s="18" t="n"/>
       <c r="R235" s="18" t="n"/>
       <c r="S235" s="18" t="n">
-        <v>0.5435112795542688</v>
+        <v>0.5752875862327042</v>
       </c>
       <c r="T235" s="17" t="n">
         <v>2.239095315024233</v>
@@ -32421,7 +32431,7 @@
       <c r="Q236" s="18" t="n"/>
       <c r="R236" s="18" t="n"/>
       <c r="S236" s="18" t="n">
-        <v>0.4606233460745066</v>
+        <v>0.4714708588482437</v>
       </c>
       <c r="T236" s="17" t="n">
         <v>2.159425367904696</v>
@@ -32513,7 +32523,7 @@
       <c r="Q237" s="18" t="n"/>
       <c r="R237" s="18" t="n"/>
       <c r="S237" s="18" t="n">
-        <v>0.6629175962152256</v>
+        <v>0.6378141927010373</v>
       </c>
       <c r="T237" s="17" t="n">
         <v>1.261363636363636</v>
@@ -32605,7 +32615,7 @@
       <c r="Q238" s="18" t="n"/>
       <c r="R238" s="18" t="n"/>
       <c r="S238" s="18" t="n">
-        <v>0.4111626402123024</v>
+        <v>0.4209450606384683</v>
       </c>
       <c r="T238" s="17" t="n">
         <v>0.8184627269215912</v>
@@ -32877,7 +32887,7 @@
       <c r="Q241" s="18" t="n"/>
       <c r="R241" s="18" t="n"/>
       <c r="S241" s="18" t="n">
-        <v>0.508951956140559</v>
+        <v>0.4967583350405974</v>
       </c>
       <c r="T241" s="17" t="n">
         <v>1.476310625175217</v>
@@ -32955,9 +32965,9 @@
       <c r="M242" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N242" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N242" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O242" s="16" t="inlineStr">
@@ -32969,7 +32979,7 @@
       <c r="Q242" s="18" t="n"/>
       <c r="R242" s="18" t="n"/>
       <c r="S242" s="18" t="n">
-        <v>0.7151137781988312</v>
+        <v>0.6455675015429797</v>
       </c>
       <c r="T242" s="17" t="n">
         <v>0.8719898605830163</v>
@@ -33047,9 +33057,9 @@
       <c r="M243" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N243" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N243" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O243" s="16" t="inlineStr">
@@ -33061,7 +33071,7 @@
       <c r="Q243" s="18" t="n"/>
       <c r="R243" s="18" t="n"/>
       <c r="S243" s="18" t="n">
-        <v>0.7126204380759479</v>
+        <v>0.6816138659823168</v>
       </c>
       <c r="T243" s="17" t="n">
         <v>4.725413223140496</v>
@@ -33153,7 +33163,7 @@
       <c r="Q244" s="18" t="n"/>
       <c r="R244" s="18" t="n"/>
       <c r="S244" s="18" t="n">
-        <v>0.6044719628515496</v>
+        <v>0.6532552232339432</v>
       </c>
       <c r="T244" s="17" t="n">
         <v>0.9018908312522298</v>
@@ -33245,7 +33255,7 @@
       <c r="Q245" s="18" t="n"/>
       <c r="R245" s="18" t="n"/>
       <c r="S245" s="18" t="n">
-        <v>0.3973915191650946</v>
+        <v>0.5623885199417042</v>
       </c>
       <c r="T245" s="17" t="n">
         <v>0.8504025044722721</v>
@@ -33323,9 +33333,9 @@
       <c r="M246" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N246" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N246" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O246" s="16" t="inlineStr">
@@ -33337,7 +33347,7 @@
       <c r="Q246" s="18" t="n"/>
       <c r="R246" s="18" t="n"/>
       <c r="S246" s="18" t="n">
-        <v>0.5305097405578191</v>
+        <v>0.7331498954342546</v>
       </c>
       <c r="T246" s="17" t="n">
         <v>0.4883318928262747</v>
@@ -33595,9 +33605,9 @@
       <c r="M249" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N249" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N249" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O249" s="16" t="inlineStr">
@@ -33608,7 +33618,9 @@
       <c r="P249" s="17" t="n"/>
       <c r="Q249" s="18" t="n"/>
       <c r="R249" s="18" t="n"/>
-      <c r="S249" s="18" t="n"/>
+      <c r="S249" s="18" t="n">
+        <v>0.5581265360732861</v>
+      </c>
       <c r="T249" s="17" t="n">
         <v>1.216171617161716</v>
       </c>
@@ -33685,9 +33697,9 @@
       <c r="M250" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N250" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N250" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O250" s="16" t="inlineStr">
@@ -33698,7 +33710,9 @@
       <c r="P250" s="17" t="n"/>
       <c r="Q250" s="18" t="n"/>
       <c r="R250" s="18" t="n"/>
-      <c r="S250" s="18" t="n"/>
+      <c r="S250" s="18" t="n">
+        <v>0.3095544449384603</v>
+      </c>
       <c r="T250" s="17" t="n">
         <v>1.018151815181518</v>
       </c>
@@ -33775,9 +33789,9 @@
       <c r="M251" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N251" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N251" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O251" s="16" t="inlineStr">
@@ -33789,7 +33803,7 @@
       <c r="Q251" s="18" t="n"/>
       <c r="R251" s="18" t="n"/>
       <c r="S251" s="18" t="n">
-        <v>0.715345937459464</v>
+        <v>0.5984128944954074</v>
       </c>
       <c r="T251" s="17" t="n">
         <v>0.4752436647173492</v>
@@ -33881,7 +33895,7 @@
       <c r="Q252" s="18" t="n"/>
       <c r="R252" s="18" t="n"/>
       <c r="S252" s="18" t="n">
-        <v>0.6204090297080062</v>
+        <v>0.5820702569979375</v>
       </c>
       <c r="T252" s="17" t="n">
         <v>1.541323792486583</v>
@@ -33973,7 +33987,7 @@
       <c r="Q253" s="18" t="n"/>
       <c r="R253" s="18" t="n"/>
       <c r="S253" s="18" t="n">
-        <v>0.5408135416248147</v>
+        <v>0.4559807841479636</v>
       </c>
       <c r="T253" s="17" t="n">
         <v>0.8495900480633307</v>
@@ -34065,7 +34079,7 @@
       <c r="Q254" s="18" t="n"/>
       <c r="R254" s="18" t="n"/>
       <c r="S254" s="18" t="n">
-        <v>0.4567359665053223</v>
+        <v>0.4169265375303701</v>
       </c>
       <c r="T254" s="17" t="n">
         <v>0.751604621309371</v>
@@ -34157,7 +34171,7 @@
       <c r="Q255" s="18" t="n"/>
       <c r="R255" s="18" t="n"/>
       <c r="S255" s="18" t="n">
-        <v>0.4333307619504696</v>
+        <v>0.5015059844954177</v>
       </c>
       <c r="T255" s="17" t="n">
         <v>1.928035982008996</v>
@@ -34695,7 +34709,7 @@
       <c r="Q261" s="18" t="n"/>
       <c r="R261" s="18" t="n"/>
       <c r="S261" s="18" t="n">
-        <v>0.5707087822924295</v>
+        <v>0.5103646712235086</v>
       </c>
       <c r="T261" s="17" t="n">
         <v>0.6269465132024374</v>
@@ -34787,7 +34801,7 @@
       <c r="Q262" s="18" t="n"/>
       <c r="R262" s="18" t="n"/>
       <c r="S262" s="18" t="n">
-        <v>0.5230348137964773</v>
+        <v>0.4890968113660506</v>
       </c>
       <c r="T262" s="17" t="n">
         <v>0.8637178720860728</v>
@@ -34879,7 +34893,7 @@
       <c r="Q263" s="18" t="n"/>
       <c r="R263" s="18" t="n"/>
       <c r="S263" s="18" t="n">
-        <v>0.6480570537091539</v>
+        <v>0.5857707379340941</v>
       </c>
       <c r="T263" s="17" t="n">
         <v>2.320116054158607</v>
@@ -35061,7 +35075,7 @@
       <c r="Q265" s="18" t="n"/>
       <c r="R265" s="18" t="n"/>
       <c r="S265" s="18" t="n">
-        <v>0.649608531187497</v>
+        <v>0.6650399697259137</v>
       </c>
       <c r="T265" s="17" t="n">
         <v>2.261082404133804</v>
@@ -35153,7 +35167,7 @@
       <c r="Q266" s="18" t="n"/>
       <c r="R266" s="18" t="n"/>
       <c r="S266" s="18" t="n">
-        <v>0.6739727982091848</v>
+        <v>0.6292492855621575</v>
       </c>
       <c r="T266" s="17" t="n">
         <v>5.408541291484435</v>
@@ -35245,7 +35259,7 @@
       <c r="Q267" s="18" t="n"/>
       <c r="R267" s="18" t="n"/>
       <c r="S267" s="18" t="n">
-        <v>0.7204076962708652</v>
+        <v>0.7758096719760381</v>
       </c>
       <c r="T267" s="17" t="n">
         <v>2.403552251135894</v>
@@ -35427,7 +35441,7 @@
       <c r="Q269" s="18" t="n"/>
       <c r="R269" s="18" t="n"/>
       <c r="S269" s="18" t="n">
-        <v>0.4692002264339888</v>
+        <v>0.4277674448457433</v>
       </c>
       <c r="T269" s="17" t="n">
         <v>0.5536398467432948</v>
@@ -35609,7 +35623,7 @@
       <c r="Q271" s="18" t="n"/>
       <c r="R271" s="18" t="n"/>
       <c r="S271" s="18" t="n">
-        <v>0.617467108411356</v>
+        <v>0.57388007113401</v>
       </c>
       <c r="T271" s="17" t="n">
         <v>2.771598808341609</v>
@@ -35687,9 +35701,9 @@
       <c r="M272" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N272" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N272" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O272" s="16" t="inlineStr">
@@ -35700,7 +35714,9 @@
       <c r="P272" s="17" t="n"/>
       <c r="Q272" s="18" t="n"/>
       <c r="R272" s="18" t="n"/>
-      <c r="S272" s="18" t="n"/>
+      <c r="S272" s="18" t="n">
+        <v>0.5788751817057183</v>
+      </c>
       <c r="T272" s="17" t="n">
         <v>1.824159021406728</v>
       </c>
@@ -35791,7 +35807,7 @@
       <c r="Q273" s="18" t="n"/>
       <c r="R273" s="18" t="n"/>
       <c r="S273" s="18" t="n">
-        <v>0.6033196111568502</v>
+        <v>0.600085483402004</v>
       </c>
       <c r="T273" s="17" t="n">
         <v>1.38828967642527</v>
@@ -35883,7 +35899,7 @@
       <c r="Q274" s="18" t="n"/>
       <c r="R274" s="18" t="n"/>
       <c r="S274" s="18" t="n">
-        <v>0.7272672506264563</v>
+        <v>0.7518991181709734</v>
       </c>
       <c r="T274" s="17" t="n">
         <v>2.377638780297108</v>
@@ -36051,9 +36067,9 @@
       <c r="M276" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N276" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N276" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O276" s="16" t="inlineStr">
@@ -36064,7 +36080,9 @@
       <c r="P276" s="17" t="n"/>
       <c r="Q276" s="18" t="n"/>
       <c r="R276" s="18" t="n"/>
-      <c r="S276" s="18" t="n"/>
+      <c r="S276" s="18" t="n">
+        <v>0.3736416048494538</v>
+      </c>
       <c r="T276" s="17" t="n">
         <v>1.323625773571169</v>
       </c>
@@ -36141,9 +36159,9 @@
       <c r="M277" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N277" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N277" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O277" s="16" t="inlineStr">
@@ -36155,7 +36173,7 @@
       <c r="Q277" s="18" t="n"/>
       <c r="R277" s="18" t="n"/>
       <c r="S277" s="18" t="n">
-        <v>0.7224757103368487</v>
+        <v>0.6635133073348529</v>
       </c>
       <c r="T277" s="17" t="n">
         <v>1.372045057908932</v>
@@ -36333,7 +36351,7 @@
       <c r="Q279" s="18" t="n"/>
       <c r="R279" s="18" t="n"/>
       <c r="S279" s="18" t="n">
-        <v>0.7493618302413245</v>
+        <v>0.7224605606425488</v>
       </c>
       <c r="T279" s="17" t="n">
         <v>7.516580855893261</v>
@@ -36425,7 +36443,7 @@
       <c r="Q280" s="18" t="n"/>
       <c r="R280" s="18" t="n"/>
       <c r="S280" s="18" t="n">
-        <v>0.5915653512145614</v>
+        <v>0.5247398532738607</v>
       </c>
       <c r="T280" s="17" t="n">
         <v>0.8738317757009346</v>
@@ -36517,7 +36535,7 @@
       <c r="Q281" s="18" t="n"/>
       <c r="R281" s="18" t="n"/>
       <c r="S281" s="18" t="n">
-        <v>0.5140102643533556</v>
+        <v>0.5737939029336211</v>
       </c>
       <c r="T281" s="17" t="n">
         <v>1.053614014426616</v>
@@ -36609,7 +36627,7 @@
       <c r="Q282" s="18" t="n"/>
       <c r="R282" s="18" t="n"/>
       <c r="S282" s="18" t="n">
-        <v>0.6170246129226069</v>
+        <v>0.6709152843774464</v>
       </c>
       <c r="T282" s="17" t="n">
         <v>0.420016406890894</v>
@@ -36701,7 +36719,7 @@
       <c r="Q283" s="18" t="n"/>
       <c r="R283" s="18" t="n"/>
       <c r="S283" s="18" t="n">
-        <v>0.7235634945354361</v>
+        <v>0.7489479118541784</v>
       </c>
       <c r="T283" s="17" t="n">
         <v>0.7697107203630176</v>
@@ -36793,7 +36811,7 @@
       <c r="Q284" s="18" t="n"/>
       <c r="R284" s="18" t="n"/>
       <c r="S284" s="18" t="n">
-        <v>0.5901896271216709</v>
+        <v>0.5537271595409039</v>
       </c>
       <c r="T284" s="17" t="n">
         <v>2.580696202531645</v>
@@ -36975,7 +36993,7 @@
       <c r="Q286" s="18" t="n"/>
       <c r="R286" s="18" t="n"/>
       <c r="S286" s="18" t="n">
-        <v>0.2167370528651828</v>
+        <v>0.2195683076456156</v>
       </c>
       <c r="T286" s="17" t="n">
         <v>0.8111008892977616</v>
@@ -37053,9 +37071,9 @@
       <c r="M287" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N287" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N287" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O287" s="16" t="inlineStr">
@@ -37066,7 +37084,9 @@
       <c r="P287" s="17" t="n"/>
       <c r="Q287" s="18" t="n"/>
       <c r="R287" s="18" t="n"/>
-      <c r="S287" s="18" t="n"/>
+      <c r="S287" s="18" t="n">
+        <v>0.4872030174395625</v>
+      </c>
       <c r="T287" s="17" t="n">
         <v>1.581815011768809</v>
       </c>
@@ -37247,7 +37267,7 @@
       <c r="Q289" s="18" t="n"/>
       <c r="R289" s="18" t="n"/>
       <c r="S289" s="18" t="n">
-        <v>0.4648445500057762</v>
+        <v>0.4609341162010514</v>
       </c>
       <c r="T289" s="17" t="n">
         <v>0.5773646801530892</v>
@@ -37339,7 +37359,7 @@
       <c r="Q290" s="18" t="n"/>
       <c r="R290" s="18" t="n"/>
       <c r="S290" s="18" t="n">
-        <v>0.4291192949280644</v>
+        <v>0.5539940747746038</v>
       </c>
       <c r="T290" s="17" t="n">
         <v>0.927188940092166</v>
@@ -37431,7 +37451,7 @@
       <c r="Q291" s="18" t="n"/>
       <c r="R291" s="18" t="n"/>
       <c r="S291" s="18" t="n">
-        <v>0.553085697824151</v>
+        <v>0.6037386078378557</v>
       </c>
       <c r="T291" s="17" t="n">
         <v>2.394088669950739</v>
@@ -37779,9 +37799,9 @@
       <c r="M295" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N295" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N295" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O295" s="16" t="inlineStr">
@@ -37793,7 +37813,7 @@
       <c r="Q295" s="18" t="n"/>
       <c r="R295" s="18" t="n"/>
       <c r="S295" s="18" t="n">
-        <v>0.6845210226952527</v>
+        <v>0.7128407916620625</v>
       </c>
       <c r="T295" s="17" t="n">
         <v>0.6223596084492529</v>
@@ -37891,7 +37911,7 @@
         <v>0.7526459</v>
       </c>
       <c r="S296" s="18" t="n">
-        <v>0.5028507992141256</v>
+        <v>0.4762835679825464</v>
       </c>
       <c r="T296" s="17" t="n">
         <v>3.715336134453782</v>
@@ -37983,7 +38003,7 @@
       <c r="Q297" s="18" t="n"/>
       <c r="R297" s="18" t="n"/>
       <c r="S297" s="18" t="n">
-        <v>0.7432773426293805</v>
+        <v>0.7283678453637008</v>
       </c>
       <c r="T297" s="17" t="n">
         <v>4.061646917654117</v>
@@ -38171,7 +38191,7 @@
         <v>0.7010222699999999</v>
       </c>
       <c r="S299" s="18" t="n">
-        <v>0.6449290757540722</v>
+        <v>0.6819513739536893</v>
       </c>
       <c r="T299" s="17" t="n">
         <v>0.7898889538281708</v>
@@ -38439,7 +38459,7 @@
       <c r="Q302" s="18" t="n"/>
       <c r="R302" s="18" t="n"/>
       <c r="S302" s="18" t="n">
-        <v>0.2610209072717398</v>
+        <v>0.2520368956354756</v>
       </c>
       <c r="T302" s="17" t="n">
         <v>0.9713307659392384</v>
@@ -38531,7 +38551,7 @@
       <c r="Q303" s="18" t="n"/>
       <c r="R303" s="18" t="n"/>
       <c r="S303" s="18" t="n">
-        <v>0.416169682313771</v>
+        <v>0.446959433581694</v>
       </c>
       <c r="T303" s="17" t="n">
         <v>3.252416356877323</v>
@@ -38623,7 +38643,7 @@
       <c r="Q304" s="18" t="n"/>
       <c r="R304" s="18" t="n"/>
       <c r="S304" s="18" t="n">
-        <v>0.5816413044122374</v>
+        <v>0.6163353788835768</v>
       </c>
       <c r="T304" s="17" t="n">
         <v>0.6243447874199184</v>
@@ -38715,7 +38735,7 @@
       <c r="Q305" s="18" t="n"/>
       <c r="R305" s="18" t="n"/>
       <c r="S305" s="18" t="n">
-        <v>0.6289936650747978</v>
+        <v>0.6309497041691718</v>
       </c>
       <c r="T305" s="17" t="n">
         <v>0.837590545177278</v>
@@ -38909,7 +38929,7 @@
         <v>0.8868774</v>
       </c>
       <c r="S307" s="18" t="n">
-        <v>0.6705342383128479</v>
+        <v>0.5956468201875351</v>
       </c>
       <c r="T307" s="17" t="n">
         <v>3.206443914081146</v>
@@ -39007,7 +39027,7 @@
         <v>0.7495296</v>
       </c>
       <c r="S308" s="18" t="n">
-        <v>0.5524332163873988</v>
+        <v>0.490577486292204</v>
       </c>
       <c r="T308" s="17" t="n">
         <v>0.5152439024390245</v>
@@ -39181,9 +39201,9 @@
       <c r="M310" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N310" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N310" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O310" s="21" t="inlineStr">
@@ -39200,9 +39220,7 @@
       <c r="R310" s="18" t="n">
         <v>0.76549137</v>
       </c>
-      <c r="S310" s="18" t="n">
-        <v>0.8011734594560863</v>
-      </c>
+      <c r="S310" s="18" t="n"/>
       <c r="T310" s="17" t="n">
         <v>0.7053276297880615</v>
       </c>
@@ -39299,7 +39317,7 @@
         <v>0.7382783000000001</v>
       </c>
       <c r="S311" s="18" t="n">
-        <v>0.1821683452120004</v>
+        <v>0.2694287207447984</v>
       </c>
       <c r="T311" s="17" t="n">
         <v>2.269461077844312</v>
@@ -39483,7 +39501,7 @@
       <c r="Q313" s="18" t="n"/>
       <c r="R313" s="18" t="n"/>
       <c r="S313" s="18" t="n">
-        <v>0.6463891976652528</v>
+        <v>0.6633289155930291</v>
       </c>
       <c r="T313" s="17" t="n">
         <v>0.8084663428174879</v>
@@ -39671,7 +39689,7 @@
       <c r="Q315" s="18" t="n"/>
       <c r="R315" s="18" t="n"/>
       <c r="S315" s="18" t="n">
-        <v>0.7117985358641741</v>
+        <v>0.7626201366377156</v>
       </c>
       <c r="T315" s="17" t="n">
         <v>2.961782234414909</v>
@@ -39763,7 +39781,7 @@
       <c r="Q316" s="18" t="n"/>
       <c r="R316" s="18" t="n"/>
       <c r="S316" s="18" t="n">
-        <v>0.8307334568965918</v>
+        <v>0.8410859612329283</v>
       </c>
       <c r="T316" s="17" t="n">
         <v>0.4333740831295842</v>
@@ -39861,7 +39879,7 @@
         <v>0.9711431</v>
       </c>
       <c r="S317" s="18" t="n">
-        <v>0.5731349163161956</v>
+        <v>0.686912538316592</v>
       </c>
       <c r="T317" s="17" t="n">
         <v>2.072112825971261</v>
@@ -40045,7 +40063,7 @@
       <c r="Q319" s="18" t="n"/>
       <c r="R319" s="18" t="n"/>
       <c r="S319" s="18" t="n">
-        <v>0.7798587485160288</v>
+        <v>0.7854513790677653</v>
       </c>
       <c r="T319" s="17" t="n">
         <v>1.067255768286696</v>
@@ -40137,7 +40155,7 @@
       <c r="Q320" s="18" t="n"/>
       <c r="R320" s="18" t="n"/>
       <c r="S320" s="18" t="n">
-        <v>0.7471226754693441</v>
+        <v>0.7586649483960702</v>
       </c>
       <c r="T320" s="17" t="n">
         <v>2.320793433652531</v>
@@ -40229,7 +40247,7 @@
       <c r="Q321" s="18" t="n"/>
       <c r="R321" s="18" t="n"/>
       <c r="S321" s="18" t="n">
-        <v>0.4773941235911519</v>
+        <v>0.5218854905271042</v>
       </c>
       <c r="T321" s="17" t="n">
         <v>2.685141158989599</v>
@@ -40307,9 +40325,9 @@
       <c r="M322" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N322" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N322" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O322" s="16" t="inlineStr">
@@ -40320,7 +40338,9 @@
       <c r="P322" s="17" t="n"/>
       <c r="Q322" s="18" t="n"/>
       <c r="R322" s="18" t="n"/>
-      <c r="S322" s="18" t="n"/>
+      <c r="S322" s="18" t="n">
+        <v>0.5436192517100052</v>
+      </c>
       <c r="T322" s="17" t="n">
         <v>0.4922143045658484</v>
       </c>
@@ -40411,7 +40431,7 @@
       <c r="Q323" s="18" t="n"/>
       <c r="R323" s="18" t="n"/>
       <c r="S323" s="18" t="n">
-        <v>0.5927597649086691</v>
+        <v>0.5186132104804776</v>
       </c>
       <c r="T323" s="17" t="n">
         <v>0.8367019570099454</v>
@@ -40503,7 +40523,7 @@
       <c r="Q324" s="18" t="n"/>
       <c r="R324" s="18" t="n"/>
       <c r="S324" s="18" t="n">
-        <v>0.5867686253479423</v>
+        <v>0.6672015237904044</v>
       </c>
       <c r="T324" s="17" t="n">
         <v>1.205399228681617</v>
@@ -40595,7 +40615,7 @@
       <c r="Q325" s="18" t="n"/>
       <c r="R325" s="18" t="n"/>
       <c r="S325" s="18" t="n">
-        <v>0.275705881758013</v>
+        <v>0.2822002711187878</v>
       </c>
       <c r="T325" s="17" t="n">
         <v>0.4254641909814323</v>
@@ -40687,7 +40707,7 @@
       <c r="Q326" s="18" t="n"/>
       <c r="R326" s="18" t="n"/>
       <c r="S326" s="18" t="n">
-        <v>0.5457667243645459</v>
+        <v>0.5477621834125371</v>
       </c>
       <c r="T326" s="17" t="n">
         <v>0.4895923677363401</v>
@@ -40861,9 +40881,9 @@
       <c r="M328" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N328" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N328" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="O328" s="16" t="inlineStr">
@@ -40874,7 +40894,9 @@
       <c r="P328" s="17" t="n"/>
       <c r="Q328" s="18" t="n"/>
       <c r="R328" s="18" t="n"/>
-      <c r="S328" s="18" t="n"/>
+      <c r="S328" s="18" t="n">
+        <v>0.2605455502191362</v>
+      </c>
       <c r="T328" s="17" t="n">
         <v>1.629464285714286</v>
       </c>
@@ -41061,7 +41083,7 @@
         <v>0.833909</v>
       </c>
       <c r="S330" s="18" t="n">
-        <v>0.5021961655740153</v>
+        <v>0.5579307369560216</v>
       </c>
       <c r="T330" s="17" t="n">
         <v>0.6043790109475276</v>
@@ -41153,7 +41175,7 @@
       <c r="Q331" s="18" t="n"/>
       <c r="R331" s="18" t="n"/>
       <c r="S331" s="18" t="n">
-        <v>0.7118551268975422</v>
+        <v>0.717636986643141</v>
       </c>
       <c r="T331" s="17" t="n">
         <v>2.239958142155679</v>
@@ -41251,7 +41273,7 @@
         <v>0.6747107</v>
       </c>
       <c r="S332" s="18" t="n">
-        <v>0.7729763176730934</v>
+        <v>0.7971105248773497</v>
       </c>
       <c r="T332" s="17" t="n">
         <v>0.754257907542579</v>
@@ -41343,7 +41365,7 @@
       <c r="Q333" s="18" t="n"/>
       <c r="R333" s="18" t="n"/>
       <c r="S333" s="18" t="n">
-        <v>0.5653823188596008</v>
+        <v>0.5812929982156705</v>
       </c>
       <c r="T333" s="17" t="n">
         <v>1.822349570200573</v>
@@ -41435,7 +41457,7 @@
       <c r="Q334" s="18" t="n"/>
       <c r="R334" s="18" t="n"/>
       <c r="S334" s="18" t="n">
-        <v>0.2771488361522261</v>
+        <v>0.2628482526089084</v>
       </c>
       <c r="T334" s="17" t="n">
         <v>1.875418060200669</v>
@@ -41513,9 +41535,9 @@
       <c r="M335" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N335" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N335" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O335" s="16" t="inlineStr">
@@ -41532,7 +41554,9 @@
       <c r="R335" s="18" t="n">
         <v>0.8674072</v>
       </c>
-      <c r="S335" s="18" t="n"/>
+      <c r="S335" s="18" t="n">
+        <v>0.7095296896933547</v>
+      </c>
       <c r="T335" s="17" t="n">
         <v>1.06591244466306</v>
       </c>
@@ -41623,7 +41647,7 @@
       <c r="Q336" s="18" t="n"/>
       <c r="R336" s="18" t="n"/>
       <c r="S336" s="18" t="n">
-        <v>0.4781446150526043</v>
+        <v>0.523578210607769</v>
       </c>
       <c r="T336" s="17" t="n">
         <v>0.6259168704156479</v>
@@ -41797,9 +41821,9 @@
       <c r="M338" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N338" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N338" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="O338" s="16" t="inlineStr">
@@ -41811,7 +41835,7 @@
       <c r="Q338" s="18" t="n"/>
       <c r="R338" s="18" t="n"/>
       <c r="S338" s="18" t="n">
-        <v>0.3107935610998545</v>
+        <v>0.2968667473323636</v>
       </c>
       <c r="T338" s="17" t="n">
         <v>1.125416944629753</v>
@@ -41903,7 +41927,7 @@
       <c r="Q339" s="18" t="n"/>
       <c r="R339" s="18" t="n"/>
       <c r="S339" s="18" t="n">
-        <v>0.6717033612318998</v>
+        <v>0.6366702441583842</v>
       </c>
       <c r="T339" s="17" t="n">
         <v>0.9376443418013858</v>
@@ -42071,9 +42095,9 @@
       <c r="M341" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N341" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N341" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O341" s="16" t="inlineStr">
@@ -42090,9 +42114,7 @@
       <c r="R341" s="18" t="n">
         <v>0.78961104</v>
       </c>
-      <c r="S341" s="18" t="n">
-        <v>0.5255549093054767</v>
-      </c>
+      <c r="S341" s="18" t="n"/>
       <c r="T341" s="17" t="n">
         <v>0.575715444328583</v>
       </c>
@@ -42183,7 +42205,7 @@
       <c r="Q342" s="18" t="n"/>
       <c r="R342" s="18" t="n"/>
       <c r="S342" s="18" t="n">
-        <v>0.7289461038143061</v>
+        <v>0.7391962541357734</v>
       </c>
       <c r="T342" s="17" t="n">
         <v>6.20915380521554</v>
@@ -42261,9 +42283,9 @@
       <c r="M343" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N343" s="13" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="N343" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O343" s="21" t="inlineStr">
@@ -42280,9 +42302,7 @@
       <c r="R343" s="18" t="n">
         <v>0.75651664</v>
       </c>
-      <c r="S343" s="18" t="n">
-        <v>0.2982371414169233</v>
-      </c>
+      <c r="S343" s="18" t="n"/>
       <c r="T343" s="17" t="n">
         <v>0.846153846153846</v>
       </c>
@@ -42373,7 +42393,7 @@
       <c r="Q344" s="18" t="n"/>
       <c r="R344" s="18" t="n"/>
       <c r="S344" s="18" t="n">
-        <v>0.5231839786298399</v>
+        <v>0.566427164681322</v>
       </c>
       <c r="T344" s="17" t="n">
         <v>0.4767295597484275</v>
@@ -42465,7 +42485,7 @@
       <c r="Q345" s="18" t="n"/>
       <c r="R345" s="18" t="n"/>
       <c r="S345" s="18" t="n">
-        <v>0.7522897609697757</v>
+        <v>0.7789712893442118</v>
       </c>
       <c r="T345" s="17" t="n">
         <v>1.48457847840987</v>
@@ -42659,7 +42679,7 @@
         <v>0.7704751</v>
       </c>
       <c r="S347" s="18" t="n">
-        <v>0.6968904447140313</v>
+        <v>0.6201804317744687</v>
       </c>
       <c r="T347" s="17" t="n">
         <v>0.4703065134099617</v>
@@ -42751,7 +42771,7 @@
       <c r="Q348" s="18" t="n"/>
       <c r="R348" s="18" t="n"/>
       <c r="S348" s="18" t="n">
-        <v>0.4094695680841484</v>
+        <v>0.3342147919272668</v>
       </c>
       <c r="T348" s="17" t="n">
         <v>0.8636972538513061</v>
@@ -42945,7 +42965,7 @@
         <v>0.7639717499999999</v>
       </c>
       <c r="S350" s="18" t="n">
-        <v>0.7423625920667569</v>
+        <v>0.7659762191223002</v>
       </c>
       <c r="T350" s="17" t="n">
         <v>1.19622307465329</v>
@@ -43037,7 +43057,7 @@
       <c r="Q351" s="18" t="n"/>
       <c r="R351" s="18" t="n"/>
       <c r="S351" s="18" t="n">
-        <v>0.4995947000052512</v>
+        <v>0.5423792557628394</v>
       </c>
       <c r="T351" s="17" t="n">
         <v>0.4658298465829846</v>
@@ -43129,7 +43149,7 @@
       <c r="Q352" s="18" t="n"/>
       <c r="R352" s="18" t="n"/>
       <c r="S352" s="18" t="n">
-        <v>0.5251604875212312</v>
+        <v>0.6502561763508388</v>
       </c>
       <c r="T352" s="17" t="n">
         <v>1.039589442815249</v>
@@ -43221,7 +43241,7 @@
       <c r="Q353" s="18" t="n"/>
       <c r="R353" s="18" t="n"/>
       <c r="S353" s="18" t="n">
-        <v>0.4105679714536018</v>
+        <v>0.35906955818219</v>
       </c>
       <c r="T353" s="17" t="n">
         <v>0.6156991005723631</v>
@@ -43319,7 +43339,7 @@
         <v>0.72540027</v>
       </c>
       <c r="S354" s="18" t="n">
-        <v>0.6170880365759566</v>
+        <v>0.6592880544574296</v>
       </c>
       <c r="T354" s="17" t="n">
         <v>1.090774786605384</v>
@@ -43417,7 +43437,7 @@
         <v>0.62487996</v>
       </c>
       <c r="S355" s="18" t="n">
-        <v>0.4598649063382162</v>
+        <v>0.4321614114527653</v>
       </c>
       <c r="T355" s="17" t="n">
         <v>0.5807496529384544</v>
@@ -43509,7 +43529,7 @@
       <c r="Q356" s="18" t="n"/>
       <c r="R356" s="18" t="n"/>
       <c r="S356" s="18" t="n">
-        <v>0.5672887014292052</v>
+        <v>0.5591422469611266</v>
       </c>
       <c r="T356" s="17" t="n">
         <v>0.6041122715404699</v>
@@ -43787,7 +43807,7 @@
       <c r="Q359" s="18" t="n"/>
       <c r="R359" s="18" t="n"/>
       <c r="S359" s="18" t="n">
-        <v>0.6127839809671252</v>
+        <v>0.6374474405786487</v>
       </c>
       <c r="T359" s="17" t="n">
         <v>2.557098588316309</v>
@@ -43879,7 +43899,7 @@
       <c r="Q360" s="18" t="n"/>
       <c r="R360" s="18" t="n"/>
       <c r="S360" s="18" t="n">
-        <v>0.5197306489197241</v>
+        <v>0.4727935181904408</v>
       </c>
       <c r="T360" s="17" t="n">
         <v>0.5620052770448549</v>
@@ -43971,7 +43991,7 @@
       <c r="Q361" s="18" t="n"/>
       <c r="R361" s="18" t="n"/>
       <c r="S361" s="18" t="n">
-        <v>0.5164834615756502</v>
+        <v>0.4844684582470855</v>
       </c>
       <c r="T361" s="17" t="n">
         <v>1.091428571428572</v>
@@ -44153,7 +44173,7 @@
       <c r="Q363" s="18" t="n"/>
       <c r="R363" s="18" t="n"/>
       <c r="S363" s="18" t="n">
-        <v>0.4628165807589738</v>
+        <v>0.5411632511771265</v>
       </c>
       <c r="T363" s="17" t="n">
         <v>2.458271236959761</v>
@@ -44341,7 +44361,7 @@
         <v>0.69375205</v>
       </c>
       <c r="S365" s="18" t="n">
-        <v>0.6491190396576128</v>
+        <v>0.5868858715233087</v>
       </c>
       <c r="T365" s="17" t="n">
         <v>0.5639419907712591</v>
@@ -44523,7 +44543,7 @@
       <c r="Q367" s="18" t="n"/>
       <c r="R367" s="18" t="n"/>
       <c r="S367" s="18" t="n">
-        <v>0.4401283204884506</v>
+        <v>0.516025613543583</v>
       </c>
       <c r="T367" s="17" t="n">
         <v>0.9496376811594204</v>
@@ -44621,7 +44641,7 @@
         <v>0.6107084</v>
       </c>
       <c r="S368" s="18" t="n">
-        <v>0.660232464303679</v>
+        <v>0.6550567465779114</v>
       </c>
       <c r="T368" s="17" t="n">
         <v>0.4339506172839507</v>
@@ -44713,7 +44733,7 @@
       <c r="Q369" s="18" t="n"/>
       <c r="R369" s="18" t="n"/>
       <c r="S369" s="18" t="n">
-        <v>0.3914088391460421</v>
+        <v>0.3469557299538398</v>
       </c>
       <c r="T369" s="17" t="n">
         <v>1.429127725856698</v>
@@ -44805,7 +44825,7 @@
       <c r="Q370" s="18" t="n"/>
       <c r="R370" s="18" t="n"/>
       <c r="S370" s="18" t="n">
-        <v>0.4947191548816678</v>
+        <v>0.4007244215092771</v>
       </c>
       <c r="T370" s="17" t="n">
         <v>2.245124113475177</v>
@@ -44897,7 +44917,7 @@
       <c r="Q371" s="18" t="n"/>
       <c r="R371" s="18" t="n"/>
       <c r="S371" s="18" t="n">
-        <v>0.5628146036595441</v>
+        <v>0.3636523539977545</v>
       </c>
       <c r="T371" s="17" t="n">
         <v>0.5865314989138306</v>
@@ -44995,7 +45015,7 @@
         <v>0.7308014</v>
       </c>
       <c r="S372" s="18" t="n">
-        <v>0.6242200942196582</v>
+        <v>0.575200412588841</v>
       </c>
       <c r="T372" s="17" t="n">
         <v>0.7280966767371602</v>
@@ -45087,7 +45107,7 @@
       <c r="Q373" s="18" t="n"/>
       <c r="R373" s="18" t="n"/>
       <c r="S373" s="18" t="n">
-        <v>0.597554780597086</v>
+        <v>0.6259000548621602</v>
       </c>
       <c r="T373" s="17" t="n">
         <v>0.7230576441102756</v>
@@ -45181,7 +45201,7 @@
         <v>0.71788675</v>
       </c>
       <c r="S374" s="18" t="n">
-        <v>0.4160303133011687</v>
+        <v>0.6383817310450381</v>
       </c>
       <c r="T374" s="17" t="n">
         <v>0.6185807656395892</v>
@@ -45359,7 +45379,7 @@
       <c r="Q376" s="18" t="n"/>
       <c r="R376" s="18" t="n"/>
       <c r="S376" s="18" t="n">
-        <v>0.4281500346594948</v>
+        <v>0.4630971414283153</v>
       </c>
       <c r="T376" s="17" t="n">
         <v>0.5206273440163656</v>
@@ -45533,9 +45553,9 @@
       <c r="M378" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N378" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N378" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O378" s="21" t="inlineStr">
@@ -45552,9 +45572,7 @@
       <c r="R378" s="18" t="n">
         <v>0.8187558</v>
       </c>
-      <c r="S378" s="18" t="n">
-        <v>0.506850885036354</v>
-      </c>
+      <c r="S378" s="18" t="n"/>
       <c r="T378" s="17" t="n">
         <v>1.210913815504547</v>
       </c>
@@ -45735,7 +45753,7 @@
       <c r="Q380" s="18" t="n"/>
       <c r="R380" s="18" t="n"/>
       <c r="S380" s="18" t="n">
-        <v>0.4980412701523086</v>
+        <v>0.4392256050468853</v>
       </c>
       <c r="T380" s="17" t="n">
         <v>0.9269051321928464</v>
@@ -45909,9 +45927,9 @@
       <c r="M382" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N382" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N382" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O382" s="21" t="inlineStr">
@@ -45929,7 +45947,7 @@
         <v>0.52328867</v>
       </c>
       <c r="S382" s="18" t="n">
-        <v>0.6950213829191962</v>
+        <v>0.7124342621711323</v>
       </c>
       <c r="T382" s="17" t="n">
         <v>0.7261663286004056</v>
@@ -46007,9 +46025,9 @@
       <c r="M383" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N383" s="13" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="N383" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O383" s="21" t="inlineStr">
@@ -46020,9 +46038,7 @@
       <c r="P383" s="17" t="n"/>
       <c r="Q383" s="18" t="n"/>
       <c r="R383" s="18" t="n"/>
-      <c r="S383" s="18" t="n">
-        <v>0.2947540646368174</v>
-      </c>
+      <c r="S383" s="18" t="n"/>
       <c r="T383" s="17" t="n">
         <v>3.76871131119865</v>
       </c>
@@ -46209,7 +46225,7 @@
       <c r="Q385" s="18" t="n"/>
       <c r="R385" s="18" t="n"/>
       <c r="S385" s="18" t="n">
-        <v>0.7455478074376765</v>
+        <v>0.7034106502074891</v>
       </c>
       <c r="T385" s="17" t="n">
         <v>1.05141065830721</v>
@@ -46301,7 +46317,7 @@
       <c r="Q386" s="18" t="n"/>
       <c r="R386" s="18" t="n"/>
       <c r="S386" s="18" t="n">
-        <v>0.7497436314897117</v>
+        <v>0.7762533026615517</v>
       </c>
       <c r="T386" s="17" t="n">
         <v>4.625858925816856</v>
@@ -46591,7 +46607,7 @@
         <v>0.9764949000000001</v>
       </c>
       <c r="S389" s="18" t="n">
-        <v>0.4909920139292872</v>
+        <v>0.4898422909695786</v>
       </c>
       <c r="T389" s="17" t="n">
         <v>0.570493753718025</v>
@@ -46683,7 +46699,7 @@
       <c r="Q390" s="18" t="n"/>
       <c r="R390" s="18" t="n"/>
       <c r="S390" s="18" t="n">
-        <v>0.5148335996434171</v>
+        <v>0.5928064745340373</v>
       </c>
       <c r="T390" s="17" t="n">
         <v>1.152542372881356</v>
@@ -46781,7 +46797,7 @@
         <v>0.6542324</v>
       </c>
       <c r="S391" s="18" t="n">
-        <v>0.6459865067797137</v>
+        <v>0.6635861240469094</v>
       </c>
       <c r="T391" s="17" t="n">
         <v>0.7472133757961783</v>
@@ -46879,7 +46895,7 @@
         <v>0.6033029600000001</v>
       </c>
       <c r="S392" s="18" t="n">
-        <v>0.4936861622579115</v>
+        <v>0.5777647275260187</v>
       </c>
       <c r="T392" s="17" t="n">
         <v>0.5043478260869565</v>
@@ -46971,7 +46987,7 @@
       <c r="Q393" s="18" t="n"/>
       <c r="R393" s="18" t="n"/>
       <c r="S393" s="18" t="n">
-        <v>0.5106620187695341</v>
+        <v>0.4156952517201482</v>
       </c>
       <c r="T393" s="17" t="n">
         <v>0.7439024390243905</v>
@@ -47069,7 +47085,7 @@
         <v>0.5687194</v>
       </c>
       <c r="S394" s="18" t="n">
-        <v>0.7222624771797724</v>
+        <v>0.7218977399594937</v>
       </c>
       <c r="T394" s="17" t="n">
         <v>3.671552660152008</v>
@@ -47163,7 +47179,7 @@
         <v>0.73038715</v>
       </c>
       <c r="S395" s="18" t="n">
-        <v>0.5137844898535688</v>
+        <v>0.5822810969826543</v>
       </c>
       <c r="T395" s="17" t="n">
         <v>0.5817855002995804</v>
@@ -47257,7 +47273,7 @@
         <v>0.75232893</v>
       </c>
       <c r="S396" s="18" t="n">
-        <v>0.6276747472115696</v>
+        <v>0.6594912617794584</v>
       </c>
       <c r="T396" s="17" t="n">
         <v>1.567424991757336</v>
@@ -47345,7 +47361,7 @@
       <c r="Q397" s="18" t="n"/>
       <c r="R397" s="18" t="n"/>
       <c r="S397" s="18" t="n">
-        <v>0.7025386886914353</v>
+        <v>0.7309212976471734</v>
       </c>
       <c r="T397" s="17" t="n">
         <v>0.7019780219780218</v>
@@ -47443,7 +47459,7 @@
         <v>1.0005956</v>
       </c>
       <c r="S398" s="18" t="n">
-        <v>0.753809399264141</v>
+        <v>0.7944271110351078</v>
       </c>
       <c r="T398" s="17" t="n">
         <v>6.526752360556281</v>
@@ -47541,7 +47557,7 @@
         <v>0.674702</v>
       </c>
       <c r="S399" s="18" t="n">
-        <v>0.6534399281483967</v>
+        <v>0.5564120547512829</v>
       </c>
       <c r="T399" s="17" t="n">
         <v>1.23574024332438</v>
@@ -47633,7 +47649,7 @@
       <c r="Q400" s="18" t="n"/>
       <c r="R400" s="18" t="n"/>
       <c r="S400" s="18" t="n">
-        <v>0.4997326456340319</v>
+        <v>0.5596067556784976</v>
       </c>
       <c r="T400" s="17" t="n">
         <v>0.8087196806877492</v>
@@ -47725,7 +47741,7 @@
       <c r="Q401" s="18" t="n"/>
       <c r="R401" s="18" t="n"/>
       <c r="S401" s="18" t="n">
-        <v>0.5546018923206325</v>
+        <v>0.6964979333509388</v>
       </c>
       <c r="T401" s="17" t="n">
         <v>2.665041782729805</v>
@@ -47803,9 +47819,9 @@
       <c r="M402" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N402" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N402" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O402" s="21" t="inlineStr">
@@ -47817,7 +47833,7 @@
       <c r="Q402" s="18" t="n"/>
       <c r="R402" s="18" t="n"/>
       <c r="S402" s="18" t="n">
-        <v>0.6897441166156211</v>
+        <v>0.7098562799680268</v>
       </c>
       <c r="T402" s="17" t="n">
         <v>1.575143892560222</v>
@@ -48011,7 +48027,7 @@
         <v>0.6387788</v>
       </c>
       <c r="S404" s="18" t="n">
-        <v>0.4544562886341274</v>
+        <v>0.5068223588068039</v>
       </c>
       <c r="T404" s="17" t="n">
         <v>0.9661595777708784</v>
@@ -48205,7 +48221,7 @@
         <v>0.4432776</v>
       </c>
       <c r="S406" s="18" t="n">
-        <v>0.5724584240352735</v>
+        <v>0.5048187603962984</v>
       </c>
       <c r="T406" s="17" t="n">
         <v>0.4347399411187438</v>
@@ -48303,7 +48319,7 @@
         <v>0.73391724</v>
       </c>
       <c r="S407" s="18" t="n">
-        <v>0.3931847116500415</v>
+        <v>0.3488617879900834</v>
       </c>
       <c r="T407" s="17" t="n">
         <v>0.7321281840591618</v>
@@ -48381,9 +48397,9 @@
       <c r="M408" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N408" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N408" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O408" s="21" t="inlineStr">
@@ -48400,7 +48416,9 @@
       <c r="R408" s="18" t="n">
         <v>0.60389733</v>
       </c>
-      <c r="S408" s="18" t="n"/>
+      <c r="S408" s="18" t="n">
+        <v>0.3669655317482515</v>
+      </c>
       <c r="T408" s="17" t="n">
         <v>1.100895036615134</v>
       </c>
@@ -48567,9 +48585,9 @@
       <c r="M410" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N410" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N410" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O410" s="16" t="inlineStr">
@@ -48581,7 +48599,7 @@
       <c r="Q410" s="18" t="n"/>
       <c r="R410" s="18" t="n"/>
       <c r="S410" s="18" t="n">
-        <v>0.6812744118045456</v>
+        <v>0.7231562230254852</v>
       </c>
       <c r="T410" s="17" t="n">
         <v>1.454699886749717</v>
@@ -48679,7 +48697,7 @@
         <v>0.5799963</v>
       </c>
       <c r="S411" s="18" t="n">
-        <v>0.4286918997954747</v>
+        <v>0.4396478218065092</v>
       </c>
       <c r="T411" s="17" t="n">
         <v>0.6679104477611939</v>
@@ -48777,7 +48795,7 @@
         <v>0.8982127</v>
       </c>
       <c r="S412" s="18" t="n">
-        <v>0.5298849977080362</v>
+        <v>0.4849383596010332</v>
       </c>
       <c r="T412" s="17" t="n">
         <v>0.7918088737201368</v>
@@ -48971,7 +48989,7 @@
         <v>0.87041146</v>
       </c>
       <c r="S414" s="18" t="n">
-        <v>0.5079579717599759</v>
+        <v>0.5024342715052236</v>
       </c>
       <c r="T414" s="17" t="n">
         <v>0.7762884651689637</v>
@@ -49049,9 +49067,9 @@
       <c r="M415" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N415" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N415" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O415" s="16" t="inlineStr">
@@ -49063,7 +49081,7 @@
       <c r="Q415" s="18" t="n"/>
       <c r="R415" s="18" t="n"/>
       <c r="S415" s="18" t="n">
-        <v>0.6859654769398358</v>
+        <v>0.711590596448634</v>
       </c>
       <c r="T415" s="17" t="n">
         <v>2.51089108910891</v>
@@ -49155,7 +49173,7 @@
       <c r="Q416" s="18" t="n"/>
       <c r="R416" s="18" t="n"/>
       <c r="S416" s="18" t="n">
-        <v>0.3803283093686726</v>
+        <v>0.3612159516046026</v>
       </c>
       <c r="T416" s="17" t="n">
         <v>3.672512938470385</v>
@@ -49433,7 +49451,7 @@
       <c r="Q419" s="18" t="n"/>
       <c r="R419" s="18" t="n"/>
       <c r="S419" s="18" t="n">
-        <v>0.5795313856606288</v>
+        <v>0.6505940492882821</v>
       </c>
       <c r="T419" s="17" t="n">
         <v>0.4678111587982834</v>
@@ -49525,7 +49543,7 @@
       <c r="Q420" s="18" t="n"/>
       <c r="R420" s="18" t="n"/>
       <c r="S420" s="18" t="n">
-        <v>0.434250404116077</v>
+        <v>0.501076758024579</v>
       </c>
       <c r="T420" s="17" t="n">
         <v>1.788079470198676</v>
@@ -49603,9 +49621,9 @@
       <c r="M421" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N421" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N421" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O421" s="21" t="inlineStr">
@@ -49617,7 +49635,7 @@
       <c r="Q421" s="18" t="n"/>
       <c r="R421" s="18" t="n"/>
       <c r="S421" s="18" t="n">
-        <v>0.7008229809992721</v>
+        <v>0.6806637665149173</v>
       </c>
       <c r="T421" s="17" t="n">
         <v>0.6722153355764124</v>
@@ -49695,9 +49713,9 @@
       <c r="M422" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N422" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N422" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O422" s="21" t="inlineStr">
@@ -49709,7 +49727,7 @@
       <c r="Q422" s="18" t="n"/>
       <c r="R422" s="18" t="n"/>
       <c r="S422" s="18" t="n">
-        <v>0.7049779263225804</v>
+        <v>0.6965497762160816</v>
       </c>
       <c r="T422" s="17" t="n">
         <v>1.549809885931559</v>
@@ -49807,7 +49825,7 @@
         <v>1.2403233</v>
       </c>
       <c r="S423" s="18" t="n">
-        <v>0.5862819999204135</v>
+        <v>0.5156456067185538</v>
       </c>
       <c r="T423" s="17" t="n">
         <v>0.4300144300144302</v>
@@ -49899,7 +49917,7 @@
       <c r="Q424" s="18" t="n"/>
       <c r="R424" s="18" t="n"/>
       <c r="S424" s="18" t="n">
-        <v>0.6058359100780947</v>
+        <v>0.5017533328740685</v>
       </c>
       <c r="T424" s="17" t="n">
         <v>1.058512513218188</v>
@@ -49977,9 +49995,9 @@
       <c r="M425" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N425" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N425" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O425" s="21" t="inlineStr">
@@ -49997,7 +50015,7 @@
         <v>0.7288751999999999</v>
       </c>
       <c r="S425" s="18" t="n">
-        <v>0.7381205259561776</v>
+        <v>0.6559055921036234</v>
       </c>
       <c r="T425" s="17" t="n">
         <v>0.6897506925207755</v>
@@ -50377,7 +50395,7 @@
         <v>0.7520978</v>
       </c>
       <c r="S429" s="18" t="n">
-        <v>0.4769474623110054</v>
+        <v>0.4373449171554189</v>
       </c>
       <c r="T429" s="17" t="n">
         <v>0.928698752228164</v>
@@ -50475,7 +50493,7 @@
         <v>0.71019286</v>
       </c>
       <c r="S430" s="18" t="n">
-        <v>0.5577103617675827</v>
+        <v>0.5685943464421359</v>
       </c>
       <c r="T430" s="17" t="n">
         <v>0.677701836821871</v>
@@ -50573,7 +50591,7 @@
         <v>0.68063307</v>
       </c>
       <c r="S431" s="18" t="n">
-        <v>0.5773915563508621</v>
+        <v>0.5204620252240071</v>
       </c>
       <c r="T431" s="17" t="n">
         <v>1.840395480225989</v>
@@ -50741,9 +50759,9 @@
       <c r="M433" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N433" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N433" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O433" s="21" t="inlineStr">
@@ -50754,9 +50772,7 @@
       <c r="P433" s="17" t="n"/>
       <c r="Q433" s="18" t="n"/>
       <c r="R433" s="18" t="n"/>
-      <c r="S433" s="18" t="n">
-        <v>0.547566424697664</v>
-      </c>
+      <c r="S433" s="18" t="n"/>
       <c r="T433" s="17" t="n">
         <v>2.1992277992278</v>
       </c>
@@ -50937,7 +50953,7 @@
       <c r="Q435" s="18" t="n"/>
       <c r="R435" s="18" t="n"/>
       <c r="S435" s="18" t="n">
-        <v>0.5126931570684803</v>
+        <v>0.6728200168433389</v>
       </c>
       <c r="T435" s="17" t="n">
         <v>0.6068376068376071</v>
@@ -51029,7 +51045,7 @@
       <c r="Q436" s="18" t="n"/>
       <c r="R436" s="18" t="n"/>
       <c r="S436" s="18" t="n">
-        <v>0.4003525942098125</v>
+        <v>0.4392510213914045</v>
       </c>
       <c r="T436" s="17" t="n">
         <v>0.914353687549564</v>
@@ -51127,7 +51143,7 @@
         <v>0.94679713</v>
       </c>
       <c r="S437" s="18" t="n">
-        <v>0.5185576902547033</v>
+        <v>0.5511850959521792</v>
       </c>
       <c r="T437" s="17" t="n">
         <v>0.6001657916551533</v>
@@ -51205,9 +51221,9 @@
       <c r="M438" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N438" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N438" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O438" s="21" t="inlineStr">
@@ -51218,7 +51234,9 @@
       <c r="P438" s="17" t="n"/>
       <c r="Q438" s="18" t="n"/>
       <c r="R438" s="18" t="n"/>
-      <c r="S438" s="18" t="n"/>
+      <c r="S438" s="18" t="n">
+        <v>0.3697001978409459</v>
+      </c>
       <c r="T438" s="17" t="n">
         <v>1.183038438071995</v>
       </c>
@@ -51309,7 +51327,7 @@
       <c r="Q439" s="18" t="n"/>
       <c r="R439" s="18" t="n"/>
       <c r="S439" s="18" t="n">
-        <v>0.336775937290926</v>
+        <v>0.3027759182392328</v>
       </c>
       <c r="T439" s="17" t="n">
         <v>2.924274593064402</v>
@@ -51779,7 +51797,7 @@
       <c r="Q444" s="18" t="n"/>
       <c r="R444" s="18" t="n"/>
       <c r="S444" s="18" t="n">
-        <v>0.4659246493560459</v>
+        <v>0.4704502563859568</v>
       </c>
       <c r="T444" s="17" t="n">
         <v>2.441651705565529</v>
@@ -51877,7 +51895,7 @@
         <v>0.84070146</v>
       </c>
       <c r="S445" s="18" t="n">
-        <v>0.4668974239876238</v>
+        <v>0.4906835230097587</v>
       </c>
       <c r="T445" s="17" t="n">
         <v>0.5459575776206578</v>
@@ -51975,7 +51993,7 @@
         <v>0.8655251</v>
       </c>
       <c r="S446" s="18" t="n">
-        <v>0.7376607580642517</v>
+        <v>0.7290991640577278</v>
       </c>
       <c r="T446" s="17" t="n">
         <v>1.521903624054162</v>
@@ -52067,7 +52085,7 @@
       <c r="Q447" s="18" t="n"/>
       <c r="R447" s="18" t="n"/>
       <c r="S447" s="18" t="n">
-        <v>0.7103344527083011</v>
+        <v>0.7179324509852756</v>
       </c>
       <c r="T447" s="17" t="n">
         <v>1.282445611402851</v>
@@ -52453,7 +52471,7 @@
         <v>0.8329916000000001</v>
       </c>
       <c r="S451" s="18" t="n">
-        <v>0.3850529301138034</v>
+        <v>0.5064397992403127</v>
       </c>
       <c r="T451" s="17" t="n">
         <v>1.586485612673779</v>
@@ -52551,7 +52569,7 @@
         <v>0.7196649000000001</v>
       </c>
       <c r="S452" s="18" t="n">
-        <v>0.5578931472211773</v>
+        <v>0.5794440811918029</v>
       </c>
       <c r="T452" s="17" t="n">
         <v>2.092882991556092</v>
@@ -52739,7 +52757,7 @@
         <v>0.53622884</v>
       </c>
       <c r="S454" s="18" t="n">
-        <v>0.5959838050142084</v>
+        <v>0.683988441089594</v>
       </c>
       <c r="T454" s="17" t="n">
         <v>0.7060518731988474</v>
@@ -52933,7 +52951,7 @@
         <v>0.74810046</v>
       </c>
       <c r="S456" s="18" t="n">
-        <v>0.7289614609543731</v>
+        <v>0.7119182458801068</v>
       </c>
       <c r="T456" s="17" t="n">
         <v>1.4359375</v>
@@ -53121,7 +53139,7 @@
       <c r="Q458" s="18" t="n"/>
       <c r="R458" s="18" t="n"/>
       <c r="S458" s="18" t="n">
-        <v>0.6728676066852537</v>
+        <v>0.6025952658760232</v>
       </c>
       <c r="T458" s="17" t="n">
         <v>1.759194734804491</v>
@@ -53213,7 +53231,7 @@
       <c r="Q459" s="18" t="n"/>
       <c r="R459" s="18" t="n"/>
       <c r="S459" s="18" t="n">
-        <v>0.4405786887710869</v>
+        <v>0.400688515279682</v>
       </c>
       <c r="T459" s="17" t="n">
         <v>2.036183584079223</v>
@@ -53381,9 +53399,9 @@
       <c r="M461" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N461" s="13" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="N461" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O461" s="21" t="inlineStr">
@@ -53401,7 +53419,7 @@
         <v>0.5567303300000001</v>
       </c>
       <c r="S461" s="18" t="n">
-        <v>0.2837494375084581</v>
+        <v>0.309543637036751</v>
       </c>
       <c r="T461" s="17" t="n">
         <v>0.6954128440366973</v>
@@ -53589,7 +53607,7 @@
       <c r="Q463" s="18" t="n"/>
       <c r="R463" s="18" t="n"/>
       <c r="S463" s="18" t="n">
-        <v>0.6440437691374272</v>
+        <v>0.695608209778855</v>
       </c>
       <c r="T463" s="17" t="n">
         <v>0.6957773512476009</v>
@@ -53687,7 +53705,7 @@
         <v>0.44510323</v>
       </c>
       <c r="S464" s="18" t="n">
-        <v>0.7397180855577336</v>
+        <v>0.7216647548345478</v>
       </c>
       <c r="T464" s="17" t="n">
         <v>1.000909504320146</v>
@@ -53765,9 +53783,9 @@
       <c r="M465" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N465" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N465" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O465" s="21" t="inlineStr">
@@ -53784,7 +53802,9 @@
       <c r="R465" s="18" t="n">
         <v>0.50870115</v>
       </c>
-      <c r="S465" s="18" t="n"/>
+      <c r="S465" s="18" t="n">
+        <v>0.4821500434156375</v>
+      </c>
       <c r="T465" s="17" t="n">
         <v>1.235971223021583</v>
       </c>
@@ -53965,7 +53985,7 @@
       <c r="Q467" s="18" t="n"/>
       <c r="R467" s="18" t="n"/>
       <c r="S467" s="18" t="n">
-        <v>0.8544781595267545</v>
+        <v>0.8446304620797814</v>
       </c>
       <c r="T467" s="17" t="n">
         <v>6.404320987654321</v>
@@ -54057,7 +54077,7 @@
       <c r="Q468" s="18" t="n"/>
       <c r="R468" s="18" t="n"/>
       <c r="S468" s="18" t="n">
-        <v>0.3896361648870775</v>
+        <v>0.3386258138955249</v>
       </c>
       <c r="T468" s="17" t="n">
         <v>0.8368657675016058</v>
@@ -54335,7 +54355,7 @@
       <c r="Q471" s="18" t="n"/>
       <c r="R471" s="18" t="n"/>
       <c r="S471" s="18" t="n">
-        <v>0.7026540545020329</v>
+        <v>0.7024241572954958</v>
       </c>
       <c r="T471" s="17" t="n">
         <v>0.6087063453025086</v>
@@ -54427,7 +54447,7 @@
       <c r="Q472" s="18" t="n"/>
       <c r="R472" s="18" t="n"/>
       <c r="S472" s="18" t="n">
-        <v>0.5137106043005844</v>
+        <v>0.4786593579210451</v>
       </c>
       <c r="T472" s="17" t="n">
         <v>0.506142506142506</v>
@@ -54525,7 +54545,7 @@
         <v>0.76183826</v>
       </c>
       <c r="S473" s="18" t="n">
-        <v>0.8332142350787368</v>
+        <v>0.7392472176403173</v>
       </c>
       <c r="T473" s="17" t="n">
         <v>1.181355068772287</v>
@@ -54617,7 +54637,7 @@
       <c r="Q474" s="18" t="n"/>
       <c r="R474" s="18" t="n"/>
       <c r="S474" s="18" t="n">
-        <v>0.6530132081073345</v>
+        <v>0.643967177440562</v>
       </c>
       <c r="T474" s="17" t="n">
         <v>0.7274746976055297</v>
@@ -54881,9 +54901,9 @@
       <c r="M477" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N477" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N477" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O477" s="16" t="inlineStr">
@@ -54900,7 +54920,9 @@
       <c r="R477" s="18" t="n">
         <v>0.72099406</v>
       </c>
-      <c r="S477" s="18" t="n"/>
+      <c r="S477" s="18" t="n">
+        <v>0.5672352307036476</v>
+      </c>
       <c r="T477" s="17" t="n">
         <v>3.41948310139165</v>
       </c>
@@ -55183,7 +55205,7 @@
       <c r="Q480" s="18" t="n"/>
       <c r="R480" s="18" t="n"/>
       <c r="S480" s="18" t="n">
-        <v>0.3765860347497871</v>
+        <v>0.4916447652864155</v>
       </c>
       <c r="T480" s="17" t="n">
         <v>1.660576923076923</v>
@@ -55377,7 +55399,7 @@
         <v>0.75757104</v>
       </c>
       <c r="S482" s="18" t="n">
-        <v>0.7094549914674084</v>
+        <v>0.7096718707964055</v>
       </c>
       <c r="T482" s="17" t="n">
         <v>2.801399144966965</v>
@@ -55475,7 +55497,7 @@
         <v>0.7516081999999999</v>
       </c>
       <c r="S483" s="18" t="n">
-        <v>0.8063845713276044</v>
+        <v>0.8274562431591108</v>
       </c>
       <c r="T483" s="17" t="n">
         <v>1.341451040081177</v>
@@ -55573,7 +55595,7 @@
         <v>0.82346135</v>
       </c>
       <c r="S484" s="18" t="n">
-        <v>0.3505931889893707</v>
+        <v>0.3447772991115003</v>
       </c>
       <c r="T484" s="17" t="n">
         <v>2.04042288557214</v>
@@ -55863,7 +55885,7 @@
         <v>0.7091786</v>
       </c>
       <c r="S487" s="18" t="n">
-        <v>0.5276018999341002</v>
+        <v>0.4781962872458785</v>
       </c>
       <c r="T487" s="17" t="n">
         <v>1.300640279394645</v>
@@ -56045,7 +56067,7 @@
       <c r="Q489" s="18" t="n"/>
       <c r="R489" s="18" t="n"/>
       <c r="S489" s="18" t="n">
-        <v>0.6362315818116375</v>
+        <v>0.5678980503892754</v>
       </c>
       <c r="T489" s="17" t="n">
         <v>2.438897673367969</v>
@@ -56143,7 +56165,7 @@
         <v>0.7968473</v>
       </c>
       <c r="S490" s="18" t="n">
-        <v>0.4228684534086355</v>
+        <v>0.6007227143021979</v>
       </c>
       <c r="T490" s="17" t="n">
         <v>0.9757852254781538</v>
@@ -56317,9 +56339,9 @@
       <c r="M492" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N492" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N492" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O492" s="21" t="inlineStr">
@@ -56331,7 +56353,7 @@
       <c r="Q492" s="18" t="n"/>
       <c r="R492" s="18" t="n"/>
       <c r="S492" s="18" t="n">
-        <v>0.701741702911972</v>
+        <v>0.6304592753253903</v>
       </c>
       <c r="T492" s="17" t="n">
         <v>1.932079414838036</v>
@@ -56409,9 +56431,9 @@
       <c r="M493" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N493" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N493" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O493" s="21" t="inlineStr">
@@ -56428,9 +56450,7 @@
       <c r="R493" s="18" t="n">
         <v>0.76133007</v>
       </c>
-      <c r="S493" s="18" t="n">
-        <v>0.48074041903763</v>
-      </c>
+      <c r="S493" s="18" t="n"/>
       <c r="T493" s="17" t="n">
         <v>0.6490020646937373</v>
       </c>
@@ -56619,7 +56639,7 @@
         <v>0.60673475</v>
       </c>
       <c r="S495" s="18" t="n">
-        <v>0.4504489499529021</v>
+        <v>0.4203943679559656</v>
       </c>
       <c r="T495" s="17" t="n">
         <v>0.822033898305085</v>
@@ -56807,7 +56827,7 @@
         <v>0.67793894</v>
       </c>
       <c r="S497" s="18" t="n">
-        <v>0.4354953198504168</v>
+        <v>0.5550667591771632</v>
       </c>
       <c r="T497" s="17" t="n">
         <v>0.59439966058549</v>
@@ -56899,7 +56919,7 @@
       <c r="Q498" s="18" t="n"/>
       <c r="R498" s="18" t="n"/>
       <c r="S498" s="18" t="n">
-        <v>0.553304009604849</v>
+        <v>0.4886766362000176</v>
       </c>
       <c r="T498" s="17" t="n">
         <v>0.5881121808287986</v>
@@ -56997,7 +57017,7 @@
         <v>0.6749991</v>
       </c>
       <c r="S499" s="18" t="n">
-        <v>0.6198759336926284</v>
+        <v>0.5894071419332365</v>
       </c>
       <c r="T499" s="17" t="n">
         <v>2.801157643854273</v>
@@ -57075,9 +57095,9 @@
       <c r="M500" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N500" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N500" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O500" s="16" t="inlineStr">
@@ -57094,7 +57114,9 @@
       <c r="R500" s="18" t="n">
         <v>0.70758593</v>
       </c>
-      <c r="S500" s="18" t="n"/>
+      <c r="S500" s="18" t="n">
+        <v>0.6144239505960996</v>
+      </c>
       <c r="T500" s="17" t="n">
         <v>3.911879259980526</v>
       </c>
@@ -57171,9 +57193,9 @@
       <c r="M501" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N501" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N501" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O501" s="21" t="inlineStr">
@@ -57191,7 +57213,7 @@
         <v>0.4818939</v>
       </c>
       <c r="S501" s="18" t="n">
-        <v>0.7235367213695357</v>
+        <v>0.6574762316204497</v>
       </c>
       <c r="T501" s="17" t="n">
         <v>1.128437173686042</v>
@@ -57289,7 +57311,7 @@
         <v>0.6915961</v>
       </c>
       <c r="S502" s="18" t="n">
-        <v>0.6340720057532938</v>
+        <v>0.5479157383489763</v>
       </c>
       <c r="T502" s="17" t="n">
         <v>2.191360294117648</v>
@@ -57483,7 +57505,7 @@
         <v>0.8065212</v>
       </c>
       <c r="S504" s="18" t="n">
-        <v>0.4506024896391161</v>
+        <v>0.3966138562959918</v>
       </c>
       <c r="T504" s="17" t="n">
         <v>0.8963242224316685</v>
@@ -57671,7 +57693,7 @@
         <v>0.9042799</v>
       </c>
       <c r="S506" s="18" t="n">
-        <v>0.8100611211445121</v>
+        <v>0.8130847444871024</v>
       </c>
       <c r="T506" s="17" t="n">
         <v>1.319507908611599</v>
@@ -57865,7 +57887,7 @@
         <v>0.6149786</v>
       </c>
       <c r="S508" s="18" t="n">
-        <v>0.5498917121269729</v>
+        <v>0.4774156269296816</v>
       </c>
       <c r="T508" s="17" t="n">
         <v>1.342245989304812</v>
@@ -57963,7 +57985,7 @@
         <v>0.50769234</v>
       </c>
       <c r="S509" s="18" t="n">
-        <v>0.5811214323072358</v>
+        <v>0.521542005659246</v>
       </c>
       <c r="T509" s="17" t="n">
         <v>1.074418604651163</v>
@@ -58433,7 +58455,7 @@
         <v>0.5481673</v>
       </c>
       <c r="S514" s="18" t="n">
-        <v>0.3813645527348297</v>
+        <v>0.3797362930987107</v>
       </c>
       <c r="T514" s="17" t="n">
         <v>0.5853567426223383</v>
@@ -58531,7 +58553,7 @@
         <v>0.6842734</v>
       </c>
       <c r="S515" s="18" t="n">
-        <v>0.4262200354933667</v>
+        <v>0.6012904356663726</v>
       </c>
       <c r="T515" s="17" t="n">
         <v>0.6191523390643741</v>
@@ -58623,7 +58645,7 @@
       <c r="Q516" s="18" t="n"/>
       <c r="R516" s="18" t="n"/>
       <c r="S516" s="18" t="n">
-        <v>0.5832511929026245</v>
+        <v>0.6851747024370571</v>
       </c>
       <c r="T516" s="17" t="n">
         <v>1.732421875</v>
@@ -58721,7 +58743,7 @@
         <v>0.818989</v>
       </c>
       <c r="S517" s="18" t="n">
-        <v>0.3586409177499345</v>
+        <v>0.3380049004997959</v>
       </c>
       <c r="T517" s="17" t="n">
         <v>3.597017268445839</v>
@@ -58909,7 +58931,7 @@
       <c r="Q519" s="18" t="n"/>
       <c r="R519" s="18" t="n"/>
       <c r="S519" s="18" t="n">
-        <v>0.7817791608225125</v>
+        <v>0.7920996823042957</v>
       </c>
       <c r="T519" s="17" t="n">
         <v>2.224081897952551</v>
@@ -59007,7 +59029,7 @@
         <v>0.8027776</v>
       </c>
       <c r="S520" s="18" t="n">
-        <v>0.5526982513274099</v>
+        <v>0.5202483596396628</v>
       </c>
       <c r="T520" s="17" t="n">
         <v>0.469123982766874</v>
@@ -59177,9 +59199,9 @@
       <c r="M522" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N522" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N522" s="15" t="inlineStr">
+        <is>
+          <t>缺失</t>
         </is>
       </c>
       <c r="O522" s="21" t="inlineStr">
@@ -59196,9 +59218,7 @@
       <c r="R522" s="18" t="n">
         <v>0.5221687</v>
       </c>
-      <c r="S522" s="18" t="n">
-        <v>0.3636718677682432</v>
-      </c>
+      <c r="S522" s="18" t="n"/>
       <c r="T522" s="17" t="n">
         <v>0.5591104174795163</v>
       </c>
@@ -59371,9 +59391,9 @@
       <c r="M524" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N524" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N524" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O524" s="21" t="inlineStr">
@@ -59390,7 +59410,9 @@
       <c r="R524" s="18" t="n">
         <v>0.57385314</v>
       </c>
-      <c r="S524" s="18" t="n"/>
+      <c r="S524" s="18" t="n">
+        <v>0.4993018158219272</v>
+      </c>
       <c r="T524" s="17" t="n">
         <v>0.956668923493568</v>
       </c>
@@ -59563,9 +59585,9 @@
       <c r="M526" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N526" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="N526" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O526" s="21" t="inlineStr">
@@ -59583,7 +59605,7 @@
         <v>0.8410945</v>
       </c>
       <c r="S526" s="18" t="n">
-        <v>0.7203721371138214</v>
+        <v>0.6731137570354445</v>
       </c>
       <c r="T526" s="17" t="n">
         <v>0.5964435663126697</v>
@@ -59661,9 +59683,9 @@
       <c r="M527" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N527" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N527" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O527" s="21" t="inlineStr">
@@ -59681,7 +59703,7 @@
         <v>0.6996871</v>
       </c>
       <c r="S527" s="18" t="n">
-        <v>0.4333990333590407</v>
+        <v>0.7131859478074142</v>
       </c>
       <c r="T527" s="17" t="n">
         <v>3.312026002166847</v>
@@ -59863,7 +59885,7 @@
       <c r="Q529" s="18" t="n"/>
       <c r="R529" s="18" t="n"/>
       <c r="S529" s="18" t="n">
-        <v>0.5385484512549878</v>
+        <v>0.5392445768765899</v>
       </c>
       <c r="T529" s="17" t="n">
         <v>1.192187242459206</v>
@@ -60141,7 +60163,7 @@
       <c r="Q532" s="18" t="n"/>
       <c r="R532" s="18" t="n"/>
       <c r="S532" s="18" t="n">
-        <v>0.516940825215523</v>
+        <v>0.4261259105615313</v>
       </c>
       <c r="T532" s="17" t="n">
         <v>1.54016620498615</v>
@@ -60239,7 +60261,7 @@
         <v>0.6943495</v>
       </c>
       <c r="S533" s="18" t="n">
-        <v>0.6030536149195881</v>
+        <v>0.5373718292354203</v>
       </c>
       <c r="T533" s="17" t="n">
         <v>1.888265019651881</v>
@@ -60331,7 +60353,7 @@
       <c r="Q534" s="18" t="n"/>
       <c r="R534" s="18" t="n"/>
       <c r="S534" s="18" t="n">
-        <v>0.7609515784199929</v>
+        <v>0.7758553780131364</v>
       </c>
       <c r="T534" s="17" t="n">
         <v>3.945628997867804</v>
@@ -60505,9 +60527,9 @@
       <c r="M536" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N536" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N536" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O536" s="21" t="inlineStr">
@@ -60525,7 +60547,7 @@
         <v>0.73734945</v>
       </c>
       <c r="S536" s="18" t="n">
-        <v>0.6820900120382728</v>
+        <v>0.7259466914775271</v>
       </c>
       <c r="T536" s="17" t="n">
         <v>2.123415046491969</v>
@@ -60707,7 +60729,7 @@
       <c r="Q538" s="18" t="n"/>
       <c r="R538" s="18" t="n"/>
       <c r="S538" s="18" t="n">
-        <v>0.6139574551083579</v>
+        <v>0.6388062126618086</v>
       </c>
       <c r="T538" s="17" t="n">
         <v>2.859574468085107</v>
@@ -60805,7 +60827,7 @@
         <v>0.45963427</v>
       </c>
       <c r="S539" s="18" t="n">
-        <v>0.4763994337920635</v>
+        <v>0.6297188347765582</v>
       </c>
       <c r="T539" s="17" t="n">
         <v>1.682291666666666</v>
@@ -60999,7 +61021,7 @@
         <v>0.7042677000000001</v>
       </c>
       <c r="S541" s="18" t="n">
-        <v>0.5935995706851601</v>
+        <v>0.527918235696316</v>
       </c>
       <c r="T541" s="17" t="n">
         <v>1.64734895191122</v>
@@ -61097,7 +61119,7 @@
         <v>0.6426842</v>
       </c>
       <c r="S542" s="18" t="n">
-        <v>0.611064512985279</v>
+        <v>0.6188727718830503</v>
       </c>
       <c r="T542" s="17" t="n">
         <v>1.886996904024768</v>
@@ -61195,7 +61217,7 @@
         <v>0.7027859</v>
       </c>
       <c r="S543" s="18" t="n">
-        <v>0.5477067413604886</v>
+        <v>0.5802070772329816</v>
       </c>
       <c r="T543" s="17" t="n">
         <v>2.776800439802089</v>
@@ -61293,7 +61315,7 @@
         <v>0.5872434399999999</v>
       </c>
       <c r="S544" s="18" t="n">
-        <v>0.5123439178560851</v>
+        <v>0.444510448628177</v>
       </c>
       <c r="T544" s="17" t="n">
         <v>3.282707622298067</v>
@@ -61391,7 +61413,7 @@
         <v>0.76738596</v>
       </c>
       <c r="S545" s="18" t="n">
-        <v>0.5095511192101143</v>
+        <v>0.4489793760771566</v>
       </c>
       <c r="T545" s="17" t="n">
         <v>1.168755595344674</v>
@@ -61489,7 +61511,7 @@
         <v>0.6656777</v>
       </c>
       <c r="S546" s="18" t="n">
-        <v>0.4666413109231236</v>
+        <v>0.4469338637317606</v>
       </c>
       <c r="T546" s="17" t="n">
         <v>0.9497019374068554</v>
@@ -61581,7 +61603,7 @@
       <c r="Q547" s="18" t="n"/>
       <c r="R547" s="18" t="n"/>
       <c r="S547" s="18" t="n">
-        <v>0.5452707285376358</v>
+        <v>0.6131655730028857</v>
       </c>
       <c r="T547" s="17" t="n">
         <v>1.410812798823096</v>
@@ -61679,7 +61701,7 @@
         <v>0.5595243</v>
       </c>
       <c r="S548" s="18" t="n">
-        <v>0.5795628496923864</v>
+        <v>0.5623725196707297</v>
       </c>
       <c r="T548" s="17" t="n">
         <v>0.9463203463203465</v>
@@ -61771,7 +61793,7 @@
       <c r="Q549" s="18" t="n"/>
       <c r="R549" s="18" t="n"/>
       <c r="S549" s="18" t="n">
-        <v>0.5210083038587118</v>
+        <v>0.5967653471702091</v>
       </c>
       <c r="T549" s="17" t="n">
         <v>1.423807816421656</v>
@@ -61935,9 +61957,9 @@
       <c r="M551" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N551" s="15" t="inlineStr">
-        <is>
-          <t>缺失</t>
+      <c r="N551" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="O551" s="21" t="inlineStr">
@@ -61954,7 +61976,9 @@
       <c r="R551" s="18" t="n">
         <v>0.5321644</v>
       </c>
-      <c r="S551" s="18" t="n"/>
+      <c r="S551" s="18" t="n">
+        <v>0.5434404800112603</v>
+      </c>
       <c r="T551" s="17" t="n">
         <v>0.7871021083092185</v>
       </c>
@@ -62243,7 +62267,7 @@
         <v>0.82397014</v>
       </c>
       <c r="S554" s="18" t="n">
-        <v>0.7695898684437974</v>
+        <v>0.7500146082164181</v>
       </c>
       <c r="T554" s="17" t="n">
         <v>2.243585383365454</v>
@@ -62629,7 +62653,7 @@
         <v>0.57138336</v>
       </c>
       <c r="S558" s="18" t="n">
-        <v>0.6019991046040267</v>
+        <v>0.5260323412006861</v>
       </c>
       <c r="T558" s="17" t="n">
         <v>0.7372621240024557</v>
@@ -62817,7 +62841,7 @@
         <v>0.8408342</v>
       </c>
       <c r="S560" s="18" t="n">
-        <v>0.7360360222329697</v>
+        <v>0.7800262910866971</v>
       </c>
       <c r="T560" s="17" t="n">
         <v>0.8023751522533493</v>
@@ -62895,9 +62919,9 @@
       <c r="M561" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N561" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="N561" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="O561" s="21" t="inlineStr">
@@ -62909,7 +62933,7 @@
       <c r="Q561" s="18" t="n"/>
       <c r="R561" s="18" t="n"/>
       <c r="S561" s="18" t="n">
-        <v>0.550599586424396</v>
+        <v>0.7261834431724031</v>
       </c>
       <c r="T561" s="17" t="n">
         <v>3.971929824561403</v>
@@ -63007,7 +63031,7 @@
         <v>0.68922967</v>
       </c>
       <c r="S562" s="18" t="n">
-        <v>0.5604782469349179</v>
+        <v>0.5797691193831117</v>
       </c>
       <c r="T562" s="17" t="n">
         <v>0.6311754684838158</v>
@@ -63105,7 +63129,7 @@
         <v>0.85952705</v>
       </c>
       <c r="S563" s="18" t="n">
-        <v>0.5869831358637251</v>
+        <v>0.5166591996391836</v>
       </c>
       <c r="T563" s="17" t="n">
         <v>1.350230414746544</v>
@@ -63197,7 +63221,7 @@
       <c r="Q564" s="18" t="n"/>
       <c r="R564" s="18" t="n"/>
       <c r="S564" s="18" t="n">
-        <v>0.575646291853504</v>
+        <v>0.5909593204072943</v>
       </c>
       <c r="T564" s="17" t="n">
         <v>1.357502908103916</v>
@@ -63769,7 +63793,7 @@
         <v>0.51964754</v>
       </c>
       <c r="S570" s="18" t="n">
-        <v>0.3363098485653065</v>
+        <v>0.3562131956424629</v>
       </c>
       <c r="T570" s="17" t="n">
         <v>2.93943661971831</v>
